--- a/AAII_Financials/Yearly/IBN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IBN_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -724,25 +724,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>14564300</v>
+        <v>14600700</v>
       </c>
       <c r="E8" s="3">
-        <v>11477400</v>
+        <v>11506100</v>
       </c>
       <c r="F8" s="3">
-        <v>10726300</v>
+        <v>10753000</v>
       </c>
       <c r="G8" s="3">
-        <v>10205700</v>
+        <v>10231200</v>
       </c>
       <c r="H8" s="3">
-        <v>8659400</v>
+        <v>8681000</v>
       </c>
       <c r="I8" s="3">
-        <v>7478100</v>
+        <v>7496800</v>
       </c>
       <c r="J8" s="3">
-        <v>7331100</v>
+        <v>7349400</v>
       </c>
       <c r="K8" s="3">
         <v>7168600</v>
@@ -994,25 +994,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-182200</v>
+        <v>-182700</v>
       </c>
       <c r="E15" s="3">
-        <v>-160000</v>
+        <v>-160400</v>
       </c>
       <c r="F15" s="3">
-        <v>-161200</v>
+        <v>-161600</v>
       </c>
       <c r="G15" s="3">
-        <v>-140900</v>
+        <v>-141200</v>
       </c>
       <c r="H15" s="3">
-        <v>-113800</v>
+        <v>-114100</v>
       </c>
       <c r="I15" s="3">
-        <v>-110900</v>
+        <v>-111200</v>
       </c>
       <c r="J15" s="3">
-        <v>-109700</v>
+        <v>-109900</v>
       </c>
       <c r="K15" s="3">
         <v>-101900</v>
@@ -1051,25 +1051,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>6747800</v>
+        <v>6764600</v>
       </c>
       <c r="E17" s="3">
-        <v>5840800</v>
+        <v>5855400</v>
       </c>
       <c r="F17" s="3">
-        <v>6554100</v>
+        <v>6570500</v>
       </c>
       <c r="G17" s="3">
-        <v>6633500</v>
+        <v>6650000</v>
       </c>
       <c r="H17" s="3">
-        <v>7131400</v>
+        <v>7149200</v>
       </c>
       <c r="I17" s="3">
-        <v>6049400</v>
+        <v>6064500</v>
       </c>
       <c r="J17" s="3">
-        <v>6084900</v>
+        <v>6100100</v>
       </c>
       <c r="K17" s="3">
         <v>5043400</v>
@@ -1093,25 +1093,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>7816500</v>
+        <v>7836000</v>
       </c>
       <c r="E18" s="3">
-        <v>5636600</v>
+        <v>5650700</v>
       </c>
       <c r="F18" s="3">
-        <v>4172100</v>
+        <v>4182600</v>
       </c>
       <c r="G18" s="3">
-        <v>3572300</v>
+        <v>3581200</v>
       </c>
       <c r="H18" s="3">
-        <v>1528000</v>
+        <v>1531800</v>
       </c>
       <c r="I18" s="3">
-        <v>1428700</v>
+        <v>1432300</v>
       </c>
       <c r="J18" s="3">
-        <v>1246200</v>
+        <v>1249300</v>
       </c>
       <c r="K18" s="3">
         <v>2125200</v>
@@ -1153,25 +1153,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2251900</v>
+        <v>-2257500</v>
       </c>
       <c r="E20" s="3">
-        <v>-1517400</v>
+        <v>-1521200</v>
       </c>
       <c r="F20" s="3">
-        <v>-1040900</v>
+        <v>-1043500</v>
       </c>
       <c r="G20" s="3">
-        <v>-1336100</v>
+        <v>-1339400</v>
       </c>
       <c r="H20" s="3">
-        <v>-636800</v>
+        <v>-638400</v>
       </c>
       <c r="I20" s="3">
-        <v>-108000</v>
+        <v>-108300</v>
       </c>
       <c r="J20" s="3">
-        <v>415100</v>
+        <v>416100</v>
       </c>
       <c r="K20" s="3">
         <v>-395800</v>
@@ -1195,25 +1195,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5762500</v>
+        <v>5777200</v>
       </c>
       <c r="E21" s="3">
-        <v>4297100</v>
+        <v>4308100</v>
       </c>
       <c r="F21" s="3">
-        <v>3308100</v>
+        <v>3316600</v>
       </c>
       <c r="G21" s="3">
-        <v>2400800</v>
+        <v>2407100</v>
       </c>
       <c r="H21" s="3">
-        <v>1016900</v>
+        <v>1019600</v>
       </c>
       <c r="I21" s="3">
-        <v>1445600</v>
+        <v>1449400</v>
       </c>
       <c r="J21" s="3">
-        <v>1786800</v>
+        <v>1791500</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>5</v>
@@ -1279,25 +1279,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>5564700</v>
+        <v>5578500</v>
       </c>
       <c r="E23" s="3">
-        <v>4119200</v>
+        <v>4129500</v>
       </c>
       <c r="F23" s="3">
-        <v>3131200</v>
+        <v>3139000</v>
       </c>
       <c r="G23" s="3">
-        <v>2236200</v>
+        <v>2241800</v>
       </c>
       <c r="H23" s="3">
-        <v>891200</v>
+        <v>893400</v>
       </c>
       <c r="I23" s="3">
-        <v>1320700</v>
+        <v>1324000</v>
       </c>
       <c r="J23" s="3">
-        <v>1661300</v>
+        <v>1665400</v>
       </c>
       <c r="K23" s="3">
         <v>1729400</v>
@@ -1321,25 +1321,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1418800</v>
+        <v>1422300</v>
       </c>
       <c r="E24" s="3">
-        <v>1017400</v>
+        <v>1020000</v>
       </c>
       <c r="F24" s="3">
-        <v>681400</v>
+        <v>683100</v>
       </c>
       <c r="G24" s="3">
-        <v>739900</v>
+        <v>741700</v>
       </c>
       <c r="H24" s="3">
-        <v>206800</v>
+        <v>207300</v>
       </c>
       <c r="I24" s="3">
-        <v>226000</v>
+        <v>226600</v>
       </c>
       <c r="J24" s="3">
-        <v>297000</v>
+        <v>297800</v>
       </c>
       <c r="K24" s="3">
         <v>408300</v>
@@ -1405,25 +1405,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>4145900</v>
+        <v>4156200</v>
       </c>
       <c r="E26" s="3">
-        <v>3101800</v>
+        <v>3109500</v>
       </c>
       <c r="F26" s="3">
-        <v>2449800</v>
+        <v>2455900</v>
       </c>
       <c r="G26" s="3">
-        <v>1496300</v>
+        <v>1500000</v>
       </c>
       <c r="H26" s="3">
-        <v>684400</v>
+        <v>686100</v>
       </c>
       <c r="I26" s="3">
-        <v>1094700</v>
+        <v>1097400</v>
       </c>
       <c r="J26" s="3">
-        <v>1364200</v>
+        <v>1367600</v>
       </c>
       <c r="K26" s="3">
         <v>1321100</v>
@@ -1447,25 +1447,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>4094600</v>
+        <v>4104800</v>
       </c>
       <c r="E27" s="3">
-        <v>3020700</v>
+        <v>3028300</v>
       </c>
       <c r="F27" s="3">
-        <v>2211600</v>
+        <v>2217100</v>
       </c>
       <c r="G27" s="3">
-        <v>1296700</v>
+        <v>1300000</v>
       </c>
       <c r="H27" s="3">
-        <v>511800</v>
+        <v>513100</v>
       </c>
       <c r="I27" s="3">
-        <v>927800</v>
+        <v>930100</v>
       </c>
       <c r="J27" s="3">
-        <v>1225700</v>
+        <v>1228700</v>
       </c>
       <c r="K27" s="3">
         <v>1230800</v>
@@ -1540,7 +1540,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="3">
-        <v>-145900</v>
+        <v>-146300</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>5</v>
@@ -1657,25 +1657,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2251900</v>
+        <v>2257500</v>
       </c>
       <c r="E32" s="3">
-        <v>1517400</v>
+        <v>1521200</v>
       </c>
       <c r="F32" s="3">
-        <v>1040900</v>
+        <v>1043500</v>
       </c>
       <c r="G32" s="3">
-        <v>1336100</v>
+        <v>1339400</v>
       </c>
       <c r="H32" s="3">
-        <v>636800</v>
+        <v>638400</v>
       </c>
       <c r="I32" s="3">
-        <v>108000</v>
+        <v>108300</v>
       </c>
       <c r="J32" s="3">
-        <v>-415100</v>
+        <v>-416100</v>
       </c>
       <c r="K32" s="3">
         <v>395800</v>
@@ -1699,25 +1699,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>4094600</v>
+        <v>4104800</v>
       </c>
       <c r="E33" s="3">
-        <v>3020700</v>
+        <v>3028300</v>
       </c>
       <c r="F33" s="3">
-        <v>2211600</v>
+        <v>2217100</v>
       </c>
       <c r="G33" s="3">
-        <v>1150800</v>
+        <v>1153700</v>
       </c>
       <c r="H33" s="3">
-        <v>511800</v>
+        <v>513100</v>
       </c>
       <c r="I33" s="3">
-        <v>927800</v>
+        <v>930100</v>
       </c>
       <c r="J33" s="3">
-        <v>1225700</v>
+        <v>1228700</v>
       </c>
       <c r="K33" s="3">
         <v>1230800</v>
@@ -1783,25 +1783,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>4094600</v>
+        <v>4104800</v>
       </c>
       <c r="E35" s="3">
-        <v>3020700</v>
+        <v>3028300</v>
       </c>
       <c r="F35" s="3">
-        <v>2211600</v>
+        <v>2217100</v>
       </c>
       <c r="G35" s="3">
-        <v>1150800</v>
+        <v>1153700</v>
       </c>
       <c r="H35" s="3">
-        <v>511800</v>
+        <v>513100</v>
       </c>
       <c r="I35" s="3">
-        <v>927800</v>
+        <v>930100</v>
       </c>
       <c r="J35" s="3">
-        <v>1225700</v>
+        <v>1228700</v>
       </c>
       <c r="K35" s="3">
         <v>1230800</v>
@@ -1908,25 +1908,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>12222500</v>
+        <v>13869900</v>
       </c>
       <c r="E41" s="3">
-        <v>11357300</v>
+        <v>14260400</v>
       </c>
       <c r="F41" s="3">
-        <v>9563500</v>
+        <v>12493000</v>
       </c>
       <c r="G41" s="3">
-        <v>6109900</v>
+        <v>6125100</v>
       </c>
       <c r="H41" s="3">
-        <v>6899800</v>
+        <v>6917100</v>
       </c>
       <c r="I41" s="3">
-        <v>6702700</v>
+        <v>6719400</v>
       </c>
       <c r="J41" s="3">
-        <v>6981000</v>
+        <v>6998400</v>
       </c>
       <c r="K41" s="3">
         <v>6136300</v>
@@ -1950,25 +1950,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>33009000</v>
+        <v>31474400</v>
       </c>
       <c r="E42" s="3">
-        <v>38237200</v>
+        <v>35457800</v>
       </c>
       <c r="F42" s="3">
-        <v>36538100</v>
+        <v>33723500</v>
       </c>
       <c r="G42" s="3">
-        <v>32938200</v>
+        <v>33020400</v>
       </c>
       <c r="H42" s="3">
-        <v>28619200</v>
+        <v>28690500</v>
       </c>
       <c r="I42" s="3">
-        <v>26812600</v>
+        <v>26879400</v>
       </c>
       <c r="J42" s="3">
-        <v>27881300</v>
+        <v>27950900</v>
       </c>
       <c r="K42" s="3">
         <v>18542900</v>
@@ -2160,25 +2160,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>241100</v>
+        <v>241700</v>
       </c>
       <c r="E47" s="3">
-        <v>241100</v>
+        <v>241700</v>
       </c>
       <c r="F47" s="3">
-        <v>80900</v>
+        <v>81100</v>
       </c>
       <c r="G47" s="3">
-        <v>83900</v>
+        <v>84100</v>
       </c>
       <c r="H47" s="3">
-        <v>87700</v>
+        <v>88000</v>
       </c>
       <c r="I47" s="3">
-        <v>59900</v>
+        <v>60100</v>
       </c>
       <c r="J47" s="3">
-        <v>45200</v>
+        <v>45300</v>
       </c>
       <c r="K47" s="3">
         <v>44700</v>
@@ -2202,25 +2202,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1319600</v>
+        <v>1322900</v>
       </c>
       <c r="E48" s="3">
-        <v>1275800</v>
+        <v>1279000</v>
       </c>
       <c r="F48" s="3">
-        <v>1300400</v>
+        <v>1303600</v>
       </c>
       <c r="G48" s="3">
-        <v>1252200</v>
+        <v>1255300</v>
       </c>
       <c r="H48" s="3">
-        <v>1162100</v>
+        <v>1165000</v>
       </c>
       <c r="I48" s="3">
-        <v>1138600</v>
+        <v>1141500</v>
       </c>
       <c r="J48" s="3">
-        <v>1123400</v>
+        <v>1126200</v>
       </c>
       <c r="K48" s="3">
         <v>1053500</v>
@@ -2250,7 +2250,7 @@
         <v>14900</v>
       </c>
       <c r="F49" s="3">
-        <v>14900</v>
+        <v>15000</v>
       </c>
       <c r="G49" s="3">
         <v>15200</v>
@@ -2259,7 +2259,7 @@
         <v>15200</v>
       </c>
       <c r="I49" s="3">
-        <v>14100</v>
+        <v>14200</v>
       </c>
       <c r="J49" s="3">
         <v>14200</v>
@@ -2370,25 +2370,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>916600</v>
+        <v>918900</v>
       </c>
       <c r="E52" s="3">
-        <v>956200</v>
+        <v>958600</v>
       </c>
       <c r="F52" s="3">
-        <v>1123000</v>
+        <v>1125800</v>
       </c>
       <c r="G52" s="3">
-        <v>1059500</v>
+        <v>1062100</v>
       </c>
       <c r="H52" s="3">
-        <v>1315800</v>
+        <v>1319000</v>
       </c>
       <c r="I52" s="3">
-        <v>940500</v>
+        <v>942900</v>
       </c>
       <c r="J52" s="3">
-        <v>1350400</v>
+        <v>1353800</v>
       </c>
       <c r="K52" s="3">
         <v>599800</v>
@@ -2454,25 +2454,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>235606000</v>
+        <v>236194000</v>
       </c>
       <c r="E54" s="3">
-        <v>210842000</v>
+        <v>211368000</v>
       </c>
       <c r="F54" s="3">
-        <v>189330000</v>
+        <v>189802000</v>
       </c>
       <c r="G54" s="3">
-        <v>165688000</v>
+        <v>166101000</v>
       </c>
       <c r="H54" s="3">
-        <v>149027000</v>
+        <v>149399000</v>
       </c>
       <c r="I54" s="3">
-        <v>135251000</v>
+        <v>135588000</v>
       </c>
       <c r="J54" s="3">
-        <v>118583000</v>
+        <v>118878000</v>
       </c>
       <c r="K54" s="3">
         <v>111078000</v>
@@ -2532,25 +2532,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3322900</v>
+        <v>3331200</v>
       </c>
       <c r="E57" s="3">
-        <v>2815400</v>
+        <v>2822400</v>
       </c>
       <c r="F57" s="3">
-        <v>4727900</v>
+        <v>4739700</v>
       </c>
       <c r="G57" s="3">
-        <v>4585900</v>
+        <v>4597300</v>
       </c>
       <c r="H57" s="3">
-        <v>4494400</v>
+        <v>4505600</v>
       </c>
       <c r="I57" s="3">
-        <v>3792200</v>
+        <v>3801600</v>
       </c>
       <c r="J57" s="3">
-        <v>3189900</v>
+        <v>3197900</v>
       </c>
       <c r="K57" s="3">
         <v>2412900</v>
@@ -2700,25 +2700,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>21564900</v>
+        <v>21618700</v>
       </c>
       <c r="E61" s="3">
-        <v>18353900</v>
+        <v>18399600</v>
       </c>
       <c r="F61" s="3">
-        <v>16803600</v>
+        <v>16845500</v>
       </c>
       <c r="G61" s="3">
-        <v>25336900</v>
+        <v>25400100</v>
       </c>
       <c r="H61" s="3">
-        <v>25072300</v>
+        <v>25134800</v>
       </c>
       <c r="I61" s="3">
-        <v>27441800</v>
+        <v>27510300</v>
       </c>
       <c r="J61" s="3">
-        <v>22505700</v>
+        <v>22561800</v>
       </c>
       <c r="K61" s="3">
         <v>26538500</v>
@@ -2742,25 +2742,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>600900</v>
+        <v>602400</v>
       </c>
       <c r="E62" s="3">
-        <v>536400</v>
+        <v>537700</v>
       </c>
       <c r="F62" s="3">
-        <v>1381000</v>
+        <v>1384400</v>
       </c>
       <c r="G62" s="3">
-        <v>796800</v>
+        <v>798800</v>
       </c>
       <c r="H62" s="3">
-        <v>378900</v>
+        <v>379800</v>
       </c>
       <c r="I62" s="3">
-        <v>343700</v>
+        <v>344600</v>
       </c>
       <c r="J62" s="3">
-        <v>307000</v>
+        <v>307800</v>
       </c>
       <c r="K62" s="3">
         <v>352800</v>
@@ -2910,25 +2910,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>209802000</v>
+        <v>210326000</v>
       </c>
       <c r="E66" s="3">
-        <v>188941000</v>
+        <v>189413000</v>
       </c>
       <c r="F66" s="3">
-        <v>170372000</v>
+        <v>170797000</v>
       </c>
       <c r="G66" s="3">
-        <v>150896000</v>
+        <v>151273000</v>
       </c>
       <c r="H66" s="3">
-        <v>135282000</v>
+        <v>135620000</v>
       </c>
       <c r="I66" s="3">
-        <v>121942000</v>
+        <v>122246000</v>
       </c>
       <c r="J66" s="3">
-        <v>105995000</v>
+        <v>106260000</v>
       </c>
       <c r="K66" s="3">
         <v>99699600</v>
@@ -3138,25 +3138,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>18625500</v>
+        <v>18672000</v>
       </c>
       <c r="E72" s="3">
-        <v>14932200</v>
+        <v>14969400</v>
       </c>
       <c r="F72" s="3">
-        <v>12156700</v>
+        <v>12187000</v>
       </c>
       <c r="G72" s="3">
-        <v>9744700</v>
+        <v>9769000</v>
       </c>
       <c r="H72" s="3">
-        <v>8875100</v>
+        <v>8897200</v>
       </c>
       <c r="I72" s="3">
-        <v>8622700</v>
+        <v>8644200</v>
       </c>
       <c r="J72" s="3">
-        <v>7948700</v>
+        <v>7968500</v>
       </c>
       <c r="K72" s="3">
         <v>6759100</v>
@@ -3306,25 +3306,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>25804100</v>
+        <v>25868400</v>
       </c>
       <c r="E76" s="3">
-        <v>21900900</v>
+        <v>21955500</v>
       </c>
       <c r="F76" s="3">
-        <v>18957800</v>
+        <v>19005100</v>
       </c>
       <c r="G76" s="3">
-        <v>14792100</v>
+        <v>14829000</v>
       </c>
       <c r="H76" s="3">
-        <v>13744700</v>
+        <v>13779000</v>
       </c>
       <c r="I76" s="3">
-        <v>13308800</v>
+        <v>13341900</v>
       </c>
       <c r="J76" s="3">
-        <v>12587200</v>
+        <v>12618600</v>
       </c>
       <c r="K76" s="3">
         <v>11378000</v>
@@ -3437,25 +3437,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>4094600</v>
+        <v>4104800</v>
       </c>
       <c r="E81" s="3">
-        <v>3020700</v>
+        <v>3028300</v>
       </c>
       <c r="F81" s="3">
-        <v>2211600</v>
+        <v>2217100</v>
       </c>
       <c r="G81" s="3">
-        <v>1150800</v>
+        <v>1153700</v>
       </c>
       <c r="H81" s="3">
-        <v>511800</v>
+        <v>513100</v>
       </c>
       <c r="I81" s="3">
-        <v>927800</v>
+        <v>930100</v>
       </c>
       <c r="J81" s="3">
-        <v>1225700</v>
+        <v>1228700</v>
       </c>
       <c r="K81" s="3">
         <v>1230800</v>
@@ -3497,25 +3497,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>198000</v>
+        <v>198500</v>
       </c>
       <c r="E83" s="3">
-        <v>178000</v>
+        <v>178400</v>
       </c>
       <c r="F83" s="3">
-        <v>177000</v>
+        <v>177400</v>
       </c>
       <c r="G83" s="3">
-        <v>164800</v>
+        <v>165200</v>
       </c>
       <c r="H83" s="3">
-        <v>125800</v>
+        <v>126100</v>
       </c>
       <c r="I83" s="3">
-        <v>125000</v>
+        <v>125300</v>
       </c>
       <c r="J83" s="3">
-        <v>125600</v>
+        <v>126000</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>5</v>
@@ -3749,25 +3749,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-453700</v>
+        <v>-454800</v>
       </c>
       <c r="E89" s="3">
-        <v>6923600</v>
+        <v>6940900</v>
       </c>
       <c r="F89" s="3">
-        <v>16603200</v>
+        <v>16644600</v>
       </c>
       <c r="G89" s="3">
-        <v>9571600</v>
+        <v>9595500</v>
       </c>
       <c r="H89" s="3">
-        <v>5855100</v>
+        <v>5869700</v>
       </c>
       <c r="I89" s="3">
-        <v>2331800</v>
+        <v>2337600</v>
       </c>
       <c r="J89" s="3">
-        <v>6332100</v>
+        <v>6347800</v>
       </c>
       <c r="K89" s="3">
         <v>-1483800</v>
@@ -3809,25 +3809,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-296900</v>
+        <v>-297600</v>
       </c>
       <c r="E91" s="3">
-        <v>-223800</v>
+        <v>-224300</v>
       </c>
       <c r="F91" s="3">
-        <v>-203100</v>
+        <v>-203600</v>
       </c>
       <c r="G91" s="3">
-        <v>-225400</v>
+        <v>-225900</v>
       </c>
       <c r="H91" s="3">
-        <v>-138100</v>
+        <v>-138500</v>
       </c>
       <c r="I91" s="3">
-        <v>-125400</v>
+        <v>-125700</v>
       </c>
       <c r="J91" s="3">
-        <v>-158400</v>
+        <v>-158800</v>
       </c>
       <c r="K91" s="3">
         <v>-150500</v>
@@ -3935,25 +3935,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-8181000</v>
+        <v>-8201400</v>
       </c>
       <c r="E94" s="3">
-        <v>-4730400</v>
+        <v>-4742200</v>
       </c>
       <c r="F94" s="3">
-        <v>-7577300</v>
+        <v>-7596200</v>
       </c>
       <c r="G94" s="3">
-        <v>-5089700</v>
+        <v>-5102400</v>
       </c>
       <c r="H94" s="3">
-        <v>-3626700</v>
+        <v>-3635800</v>
       </c>
       <c r="I94" s="3">
-        <v>-6084000</v>
+        <v>-6099200</v>
       </c>
       <c r="J94" s="3">
-        <v>-193200</v>
+        <v>-193700</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>5</v>
@@ -3995,25 +3995,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-418600</v>
+        <v>-419600</v>
       </c>
       <c r="E96" s="3">
-        <v>-166600</v>
+        <v>-167100</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-106600</v>
+        <v>-106900</v>
       </c>
       <c r="H96" s="3">
-        <v>-140600</v>
+        <v>-141000</v>
       </c>
       <c r="I96" s="3">
-        <v>-206400</v>
+        <v>-207000</v>
       </c>
       <c r="J96" s="3">
-        <v>-411800</v>
+        <v>-412800</v>
       </c>
       <c r="K96" s="3">
         <v>-372900</v>
@@ -4163,25 +4163,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>2982300</v>
+        <v>2989800</v>
       </c>
       <c r="E100" s="3">
-        <v>2099400</v>
+        <v>2104600</v>
       </c>
       <c r="F100" s="3">
-        <v>-6576400</v>
+        <v>-6592800</v>
       </c>
       <c r="G100" s="3">
-        <v>360000</v>
+        <v>360900</v>
       </c>
       <c r="H100" s="3">
-        <v>-2405700</v>
+        <v>-2411700</v>
       </c>
       <c r="I100" s="3">
-        <v>4773000</v>
+        <v>4784900</v>
       </c>
       <c r="J100" s="3">
-        <v>-4267000</v>
+        <v>-4277600</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>5</v>
@@ -4211,16 +4211,16 @@
         <v>-15300</v>
       </c>
       <c r="F101" s="3">
-        <v>-77500</v>
+        <v>-77700</v>
       </c>
       <c r="G101" s="3">
-        <v>25700</v>
+        <v>25800</v>
       </c>
       <c r="H101" s="3">
         <v>-16200</v>
       </c>
       <c r="I101" s="3">
-        <v>2700</v>
+        <v>2800</v>
       </c>
       <c r="J101" s="3">
         <v>-12700</v>
@@ -4247,25 +4247,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-5614300</v>
+        <v>-5628300</v>
       </c>
       <c r="E102" s="3">
-        <v>4277300</v>
+        <v>4288000</v>
       </c>
       <c r="F102" s="3">
-        <v>2372000</v>
+        <v>2377900</v>
       </c>
       <c r="G102" s="3">
-        <v>4867600</v>
+        <v>4879700</v>
       </c>
       <c r="H102" s="3">
-        <v>-193500</v>
+        <v>-194000</v>
       </c>
       <c r="I102" s="3">
-        <v>1023500</v>
+        <v>1026100</v>
       </c>
       <c r="J102" s="3">
-        <v>1859200</v>
+        <v>1863900</v>
       </c>
       <c r="K102" s="3">
         <v>-75100</v>

--- a/AAII_Financials/Yearly/IBN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IBN_YR_FIN.xlsx
@@ -724,25 +724,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>14600700</v>
+        <v>14515900</v>
       </c>
       <c r="E8" s="3">
-        <v>11506100</v>
+        <v>11439300</v>
       </c>
       <c r="F8" s="3">
-        <v>10753000</v>
+        <v>10690600</v>
       </c>
       <c r="G8" s="3">
-        <v>10231200</v>
+        <v>10171800</v>
       </c>
       <c r="H8" s="3">
-        <v>8681000</v>
+        <v>8630600</v>
       </c>
       <c r="I8" s="3">
-        <v>7496800</v>
+        <v>7453300</v>
       </c>
       <c r="J8" s="3">
-        <v>7349400</v>
+        <v>7306700</v>
       </c>
       <c r="K8" s="3">
         <v>7168600</v>
@@ -994,25 +994,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-182700</v>
+        <v>-181600</v>
       </c>
       <c r="E15" s="3">
-        <v>-160400</v>
+        <v>-159500</v>
       </c>
       <c r="F15" s="3">
-        <v>-161600</v>
+        <v>-160700</v>
       </c>
       <c r="G15" s="3">
-        <v>-141200</v>
+        <v>-140400</v>
       </c>
       <c r="H15" s="3">
-        <v>-114100</v>
+        <v>-113400</v>
       </c>
       <c r="I15" s="3">
-        <v>-111200</v>
+        <v>-110600</v>
       </c>
       <c r="J15" s="3">
-        <v>-109900</v>
+        <v>-109300</v>
       </c>
       <c r="K15" s="3">
         <v>-101900</v>
@@ -1051,25 +1051,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>6764600</v>
+        <v>6725400</v>
       </c>
       <c r="E17" s="3">
-        <v>5855400</v>
+        <v>5821400</v>
       </c>
       <c r="F17" s="3">
-        <v>6570500</v>
+        <v>6532300</v>
       </c>
       <c r="G17" s="3">
-        <v>6650000</v>
+        <v>6611400</v>
       </c>
       <c r="H17" s="3">
-        <v>7149200</v>
+        <v>7107700</v>
       </c>
       <c r="I17" s="3">
-        <v>6064500</v>
+        <v>6029300</v>
       </c>
       <c r="J17" s="3">
-        <v>6100100</v>
+        <v>6064700</v>
       </c>
       <c r="K17" s="3">
         <v>5043400</v>
@@ -1093,25 +1093,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>7836000</v>
+        <v>7790500</v>
       </c>
       <c r="E18" s="3">
-        <v>5650700</v>
+        <v>5617900</v>
       </c>
       <c r="F18" s="3">
-        <v>4182600</v>
+        <v>4158300</v>
       </c>
       <c r="G18" s="3">
-        <v>3581200</v>
+        <v>3560400</v>
       </c>
       <c r="H18" s="3">
-        <v>1531800</v>
+        <v>1522900</v>
       </c>
       <c r="I18" s="3">
-        <v>1432300</v>
+        <v>1424000</v>
       </c>
       <c r="J18" s="3">
-        <v>1249300</v>
+        <v>1242000</v>
       </c>
       <c r="K18" s="3">
         <v>2125200</v>
@@ -1153,25 +1153,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2257500</v>
+        <v>-2244400</v>
       </c>
       <c r="E20" s="3">
-        <v>-1521200</v>
+        <v>-1512400</v>
       </c>
       <c r="F20" s="3">
-        <v>-1043500</v>
+        <v>-1037500</v>
       </c>
       <c r="G20" s="3">
-        <v>-1339400</v>
+        <v>-1331600</v>
       </c>
       <c r="H20" s="3">
-        <v>-638400</v>
+        <v>-634700</v>
       </c>
       <c r="I20" s="3">
-        <v>-108300</v>
+        <v>-107600</v>
       </c>
       <c r="J20" s="3">
-        <v>416100</v>
+        <v>413700</v>
       </c>
       <c r="K20" s="3">
         <v>-395800</v>
@@ -1195,25 +1195,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5777200</v>
+        <v>5743000</v>
       </c>
       <c r="E21" s="3">
-        <v>4308100</v>
+        <v>4282500</v>
       </c>
       <c r="F21" s="3">
-        <v>3316600</v>
+        <v>3296800</v>
       </c>
       <c r="G21" s="3">
-        <v>2407100</v>
+        <v>2392600</v>
       </c>
       <c r="H21" s="3">
-        <v>1019600</v>
+        <v>1013300</v>
       </c>
       <c r="I21" s="3">
-        <v>1449400</v>
+        <v>1440600</v>
       </c>
       <c r="J21" s="3">
-        <v>1791500</v>
+        <v>1780700</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>5</v>
@@ -1279,25 +1279,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>5578500</v>
+        <v>5546200</v>
       </c>
       <c r="E23" s="3">
-        <v>4129500</v>
+        <v>4105500</v>
       </c>
       <c r="F23" s="3">
-        <v>3139000</v>
+        <v>3120800</v>
       </c>
       <c r="G23" s="3">
-        <v>2241800</v>
+        <v>2228800</v>
       </c>
       <c r="H23" s="3">
-        <v>893400</v>
+        <v>888300</v>
       </c>
       <c r="I23" s="3">
-        <v>1324000</v>
+        <v>1316300</v>
       </c>
       <c r="J23" s="3">
-        <v>1665400</v>
+        <v>1655700</v>
       </c>
       <c r="K23" s="3">
         <v>1729400</v>
@@ -1321,25 +1321,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1422300</v>
+        <v>1414000</v>
       </c>
       <c r="E24" s="3">
-        <v>1020000</v>
+        <v>1014000</v>
       </c>
       <c r="F24" s="3">
-        <v>683100</v>
+        <v>679200</v>
       </c>
       <c r="G24" s="3">
-        <v>741700</v>
+        <v>737400</v>
       </c>
       <c r="H24" s="3">
-        <v>207300</v>
+        <v>206100</v>
       </c>
       <c r="I24" s="3">
-        <v>226600</v>
+        <v>225300</v>
       </c>
       <c r="J24" s="3">
-        <v>297800</v>
+        <v>296000</v>
       </c>
       <c r="K24" s="3">
         <v>408300</v>
@@ -1405,25 +1405,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>4156200</v>
+        <v>4132100</v>
       </c>
       <c r="E26" s="3">
-        <v>3109500</v>
+        <v>3091500</v>
       </c>
       <c r="F26" s="3">
-        <v>2455900</v>
+        <v>2441600</v>
       </c>
       <c r="G26" s="3">
-        <v>1500000</v>
+        <v>1491300</v>
       </c>
       <c r="H26" s="3">
-        <v>686100</v>
+        <v>682100</v>
       </c>
       <c r="I26" s="3">
-        <v>1097400</v>
+        <v>1091000</v>
       </c>
       <c r="J26" s="3">
-        <v>1367600</v>
+        <v>1359700</v>
       </c>
       <c r="K26" s="3">
         <v>1321100</v>
@@ -1447,25 +1447,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>4104800</v>
+        <v>4081000</v>
       </c>
       <c r="E27" s="3">
-        <v>3028300</v>
+        <v>3010700</v>
       </c>
       <c r="F27" s="3">
-        <v>2217100</v>
+        <v>2204300</v>
       </c>
       <c r="G27" s="3">
-        <v>1300000</v>
+        <v>1292400</v>
       </c>
       <c r="H27" s="3">
-        <v>513100</v>
+        <v>510100</v>
       </c>
       <c r="I27" s="3">
-        <v>930100</v>
+        <v>924700</v>
       </c>
       <c r="J27" s="3">
-        <v>1228700</v>
+        <v>1221600</v>
       </c>
       <c r="K27" s="3">
         <v>1230800</v>
@@ -1540,7 +1540,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="3">
-        <v>-146300</v>
+        <v>-145400</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>5</v>
@@ -1657,25 +1657,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2257500</v>
+        <v>2244400</v>
       </c>
       <c r="E32" s="3">
-        <v>1521200</v>
+        <v>1512400</v>
       </c>
       <c r="F32" s="3">
-        <v>1043500</v>
+        <v>1037500</v>
       </c>
       <c r="G32" s="3">
-        <v>1339400</v>
+        <v>1331600</v>
       </c>
       <c r="H32" s="3">
-        <v>638400</v>
+        <v>634700</v>
       </c>
       <c r="I32" s="3">
-        <v>108300</v>
+        <v>107600</v>
       </c>
       <c r="J32" s="3">
-        <v>-416100</v>
+        <v>-413700</v>
       </c>
       <c r="K32" s="3">
         <v>395800</v>
@@ -1699,25 +1699,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>4104800</v>
+        <v>4081000</v>
       </c>
       <c r="E33" s="3">
-        <v>3028300</v>
+        <v>3010700</v>
       </c>
       <c r="F33" s="3">
-        <v>2217100</v>
+        <v>2204300</v>
       </c>
       <c r="G33" s="3">
-        <v>1153700</v>
+        <v>1147000</v>
       </c>
       <c r="H33" s="3">
-        <v>513100</v>
+        <v>510100</v>
       </c>
       <c r="I33" s="3">
-        <v>930100</v>
+        <v>924700</v>
       </c>
       <c r="J33" s="3">
-        <v>1228700</v>
+        <v>1221600</v>
       </c>
       <c r="K33" s="3">
         <v>1230800</v>
@@ -1783,25 +1783,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>4104800</v>
+        <v>4081000</v>
       </c>
       <c r="E35" s="3">
-        <v>3028300</v>
+        <v>3010700</v>
       </c>
       <c r="F35" s="3">
-        <v>2217100</v>
+        <v>2204300</v>
       </c>
       <c r="G35" s="3">
-        <v>1153700</v>
+        <v>1147000</v>
       </c>
       <c r="H35" s="3">
-        <v>513100</v>
+        <v>510100</v>
       </c>
       <c r="I35" s="3">
-        <v>930100</v>
+        <v>924700</v>
       </c>
       <c r="J35" s="3">
-        <v>1228700</v>
+        <v>1221600</v>
       </c>
       <c r="K35" s="3">
         <v>1230800</v>
@@ -1908,25 +1908,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>13869900</v>
+        <v>13789400</v>
       </c>
       <c r="E41" s="3">
-        <v>14260400</v>
+        <v>14177600</v>
       </c>
       <c r="F41" s="3">
-        <v>12493000</v>
+        <v>12420500</v>
       </c>
       <c r="G41" s="3">
-        <v>6125100</v>
+        <v>6089600</v>
       </c>
       <c r="H41" s="3">
-        <v>6917100</v>
+        <v>6876900</v>
       </c>
       <c r="I41" s="3">
-        <v>6719400</v>
+        <v>6680400</v>
       </c>
       <c r="J41" s="3">
-        <v>6998400</v>
+        <v>6957800</v>
       </c>
       <c r="K41" s="3">
         <v>6136300</v>
@@ -1950,25 +1950,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>31474400</v>
+        <v>31291800</v>
       </c>
       <c r="E42" s="3">
-        <v>35457800</v>
+        <v>35252000</v>
       </c>
       <c r="F42" s="3">
-        <v>33723500</v>
+        <v>33527700</v>
       </c>
       <c r="G42" s="3">
-        <v>33020400</v>
+        <v>32828700</v>
       </c>
       <c r="H42" s="3">
-        <v>28690500</v>
+        <v>28524000</v>
       </c>
       <c r="I42" s="3">
-        <v>26879400</v>
+        <v>26723400</v>
       </c>
       <c r="J42" s="3">
-        <v>27950900</v>
+        <v>27788600</v>
       </c>
       <c r="K42" s="3">
         <v>18542900</v>
@@ -2160,25 +2160,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>241700</v>
+        <v>240300</v>
       </c>
       <c r="E47" s="3">
-        <v>241700</v>
+        <v>240300</v>
       </c>
       <c r="F47" s="3">
-        <v>81100</v>
+        <v>80600</v>
       </c>
       <c r="G47" s="3">
-        <v>84100</v>
+        <v>83600</v>
       </c>
       <c r="H47" s="3">
-        <v>88000</v>
+        <v>87400</v>
       </c>
       <c r="I47" s="3">
-        <v>60100</v>
+        <v>59700</v>
       </c>
       <c r="J47" s="3">
-        <v>45300</v>
+        <v>45100</v>
       </c>
       <c r="K47" s="3">
         <v>44700</v>
@@ -2202,25 +2202,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1322900</v>
+        <v>1315200</v>
       </c>
       <c r="E48" s="3">
-        <v>1279000</v>
+        <v>1271600</v>
       </c>
       <c r="F48" s="3">
-        <v>1303600</v>
+        <v>1296000</v>
       </c>
       <c r="G48" s="3">
-        <v>1255300</v>
+        <v>1248000</v>
       </c>
       <c r="H48" s="3">
-        <v>1165000</v>
+        <v>1158300</v>
       </c>
       <c r="I48" s="3">
-        <v>1141500</v>
+        <v>1134900</v>
       </c>
       <c r="J48" s="3">
-        <v>1126200</v>
+        <v>1119600</v>
       </c>
       <c r="K48" s="3">
         <v>1053500</v>
@@ -2244,22 +2244,22 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E49" s="3">
+        <v>14800</v>
+      </c>
+      <c r="F49" s="3">
         <v>14900</v>
       </c>
-      <c r="E49" s="3">
-        <v>14900</v>
-      </c>
-      <c r="F49" s="3">
-        <v>15000</v>
-      </c>
       <c r="G49" s="3">
-        <v>15200</v>
+        <v>15100</v>
       </c>
       <c r="H49" s="3">
-        <v>15200</v>
+        <v>15100</v>
       </c>
       <c r="I49" s="3">
-        <v>14200</v>
+        <v>14100</v>
       </c>
       <c r="J49" s="3">
         <v>14200</v>
@@ -2370,25 +2370,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>918900</v>
+        <v>913600</v>
       </c>
       <c r="E52" s="3">
-        <v>958600</v>
+        <v>953000</v>
       </c>
       <c r="F52" s="3">
-        <v>1125800</v>
+        <v>1119300</v>
       </c>
       <c r="G52" s="3">
-        <v>1062100</v>
+        <v>1056000</v>
       </c>
       <c r="H52" s="3">
-        <v>1319000</v>
+        <v>1311400</v>
       </c>
       <c r="I52" s="3">
-        <v>942900</v>
+        <v>937400</v>
       </c>
       <c r="J52" s="3">
-        <v>1353800</v>
+        <v>1346000</v>
       </c>
       <c r="K52" s="3">
         <v>599800</v>
@@ -2454,25 +2454,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>236194000</v>
+        <v>234823000</v>
       </c>
       <c r="E54" s="3">
-        <v>211368000</v>
+        <v>210141000</v>
       </c>
       <c r="F54" s="3">
-        <v>189802000</v>
+        <v>188700000</v>
       </c>
       <c r="G54" s="3">
-        <v>166101000</v>
+        <v>165137000</v>
       </c>
       <c r="H54" s="3">
-        <v>149399000</v>
+        <v>148531000</v>
       </c>
       <c r="I54" s="3">
-        <v>135588000</v>
+        <v>134801000</v>
       </c>
       <c r="J54" s="3">
-        <v>118878000</v>
+        <v>118188000</v>
       </c>
       <c r="K54" s="3">
         <v>111078000</v>
@@ -2532,25 +2532,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3331200</v>
+        <v>3311900</v>
       </c>
       <c r="E57" s="3">
-        <v>2822400</v>
+        <v>2806000</v>
       </c>
       <c r="F57" s="3">
-        <v>4739700</v>
+        <v>4712200</v>
       </c>
       <c r="G57" s="3">
-        <v>4597300</v>
+        <v>4570600</v>
       </c>
       <c r="H57" s="3">
-        <v>4505600</v>
+        <v>4479500</v>
       </c>
       <c r="I57" s="3">
-        <v>3801600</v>
+        <v>3779500</v>
       </c>
       <c r="J57" s="3">
-        <v>3197900</v>
+        <v>3179300</v>
       </c>
       <c r="K57" s="3">
         <v>2412900</v>
@@ -2700,25 +2700,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>21618700</v>
+        <v>21493200</v>
       </c>
       <c r="E61" s="3">
-        <v>18399600</v>
+        <v>18292800</v>
       </c>
       <c r="F61" s="3">
-        <v>16845500</v>
+        <v>16747800</v>
       </c>
       <c r="G61" s="3">
-        <v>25400100</v>
+        <v>25252700</v>
       </c>
       <c r="H61" s="3">
-        <v>25134800</v>
+        <v>24988900</v>
       </c>
       <c r="I61" s="3">
-        <v>27510300</v>
+        <v>27350600</v>
       </c>
       <c r="J61" s="3">
-        <v>22561800</v>
+        <v>22430800</v>
       </c>
       <c r="K61" s="3">
         <v>26538500</v>
@@ -2742,25 +2742,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>602400</v>
+        <v>598900</v>
       </c>
       <c r="E62" s="3">
-        <v>537700</v>
+        <v>534600</v>
       </c>
       <c r="F62" s="3">
-        <v>1384400</v>
+        <v>1376400</v>
       </c>
       <c r="G62" s="3">
-        <v>798800</v>
+        <v>794200</v>
       </c>
       <c r="H62" s="3">
-        <v>379800</v>
+        <v>377600</v>
       </c>
       <c r="I62" s="3">
-        <v>344600</v>
+        <v>342600</v>
       </c>
       <c r="J62" s="3">
-        <v>307800</v>
+        <v>306000</v>
       </c>
       <c r="K62" s="3">
         <v>352800</v>
@@ -2910,25 +2910,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>210326000</v>
+        <v>209105000</v>
       </c>
       <c r="E66" s="3">
-        <v>189413000</v>
+        <v>188313000</v>
       </c>
       <c r="F66" s="3">
-        <v>170797000</v>
+        <v>169805000</v>
       </c>
       <c r="G66" s="3">
-        <v>151273000</v>
+        <v>150394000</v>
       </c>
       <c r="H66" s="3">
-        <v>135620000</v>
+        <v>134832000</v>
       </c>
       <c r="I66" s="3">
-        <v>122246000</v>
+        <v>121537000</v>
       </c>
       <c r="J66" s="3">
-        <v>106260000</v>
+        <v>105643000</v>
       </c>
       <c r="K66" s="3">
         <v>99699600</v>
@@ -3138,25 +3138,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>18672000</v>
+        <v>18563600</v>
       </c>
       <c r="E72" s="3">
-        <v>14969400</v>
+        <v>14882500</v>
       </c>
       <c r="F72" s="3">
-        <v>12187000</v>
+        <v>12116300</v>
       </c>
       <c r="G72" s="3">
-        <v>9769000</v>
+        <v>9712300</v>
       </c>
       <c r="H72" s="3">
-        <v>8897200</v>
+        <v>8845600</v>
       </c>
       <c r="I72" s="3">
-        <v>8644200</v>
+        <v>8594000</v>
       </c>
       <c r="J72" s="3">
-        <v>7968500</v>
+        <v>7922300</v>
       </c>
       <c r="K72" s="3">
         <v>6759100</v>
@@ -3306,25 +3306,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>25868400</v>
+        <v>25718300</v>
       </c>
       <c r="E76" s="3">
-        <v>21955500</v>
+        <v>21828100</v>
       </c>
       <c r="F76" s="3">
-        <v>19005100</v>
+        <v>18894700</v>
       </c>
       <c r="G76" s="3">
-        <v>14829000</v>
+        <v>14742900</v>
       </c>
       <c r="H76" s="3">
-        <v>13779000</v>
+        <v>13699000</v>
       </c>
       <c r="I76" s="3">
-        <v>13341900</v>
+        <v>13264500</v>
       </c>
       <c r="J76" s="3">
-        <v>12618600</v>
+        <v>12545400</v>
       </c>
       <c r="K76" s="3">
         <v>11378000</v>
@@ -3437,25 +3437,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>4104800</v>
+        <v>4081000</v>
       </c>
       <c r="E81" s="3">
-        <v>3028300</v>
+        <v>3010700</v>
       </c>
       <c r="F81" s="3">
-        <v>2217100</v>
+        <v>2204300</v>
       </c>
       <c r="G81" s="3">
-        <v>1153700</v>
+        <v>1147000</v>
       </c>
       <c r="H81" s="3">
-        <v>513100</v>
+        <v>510100</v>
       </c>
       <c r="I81" s="3">
-        <v>930100</v>
+        <v>924700</v>
       </c>
       <c r="J81" s="3">
-        <v>1228700</v>
+        <v>1221600</v>
       </c>
       <c r="K81" s="3">
         <v>1230800</v>
@@ -3497,25 +3497,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>198500</v>
+        <v>197300</v>
       </c>
       <c r="E83" s="3">
-        <v>178400</v>
+        <v>177400</v>
       </c>
       <c r="F83" s="3">
-        <v>177400</v>
+        <v>176400</v>
       </c>
       <c r="G83" s="3">
-        <v>165200</v>
+        <v>164200</v>
       </c>
       <c r="H83" s="3">
-        <v>126100</v>
+        <v>125300</v>
       </c>
       <c r="I83" s="3">
-        <v>125300</v>
+        <v>124600</v>
       </c>
       <c r="J83" s="3">
-        <v>126000</v>
+        <v>125200</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>5</v>
@@ -3749,25 +3749,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-454800</v>
+        <v>-452200</v>
       </c>
       <c r="E89" s="3">
-        <v>6940900</v>
+        <v>6900600</v>
       </c>
       <c r="F89" s="3">
-        <v>16644600</v>
+        <v>16548000</v>
       </c>
       <c r="G89" s="3">
-        <v>9595500</v>
+        <v>9539800</v>
       </c>
       <c r="H89" s="3">
-        <v>5869700</v>
+        <v>5835700</v>
       </c>
       <c r="I89" s="3">
-        <v>2337600</v>
+        <v>2324000</v>
       </c>
       <c r="J89" s="3">
-        <v>6347800</v>
+        <v>6311000</v>
       </c>
       <c r="K89" s="3">
         <v>-1483800</v>
@@ -3809,25 +3809,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-297600</v>
+        <v>-295900</v>
       </c>
       <c r="E91" s="3">
-        <v>-224300</v>
+        <v>-223000</v>
       </c>
       <c r="F91" s="3">
-        <v>-203600</v>
+        <v>-202400</v>
       </c>
       <c r="G91" s="3">
-        <v>-225900</v>
+        <v>-224600</v>
       </c>
       <c r="H91" s="3">
-        <v>-138500</v>
+        <v>-137700</v>
       </c>
       <c r="I91" s="3">
-        <v>-125700</v>
+        <v>-125000</v>
       </c>
       <c r="J91" s="3">
-        <v>-158800</v>
+        <v>-157900</v>
       </c>
       <c r="K91" s="3">
         <v>-150500</v>
@@ -3935,25 +3935,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-8201400</v>
+        <v>-8153800</v>
       </c>
       <c r="E94" s="3">
-        <v>-4742200</v>
+        <v>-4714600</v>
       </c>
       <c r="F94" s="3">
-        <v>-7596200</v>
+        <v>-7552100</v>
       </c>
       <c r="G94" s="3">
-        <v>-5102400</v>
+        <v>-5072800</v>
       </c>
       <c r="H94" s="3">
-        <v>-3635800</v>
+        <v>-3614700</v>
       </c>
       <c r="I94" s="3">
-        <v>-6099200</v>
+        <v>-6063800</v>
       </c>
       <c r="J94" s="3">
-        <v>-193700</v>
+        <v>-192500</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>5</v>
@@ -3995,25 +3995,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-419600</v>
+        <v>-417200</v>
       </c>
       <c r="E96" s="3">
-        <v>-167100</v>
+        <v>-166100</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-106900</v>
+        <v>-106300</v>
       </c>
       <c r="H96" s="3">
-        <v>-141000</v>
+        <v>-140100</v>
       </c>
       <c r="I96" s="3">
-        <v>-207000</v>
+        <v>-205800</v>
       </c>
       <c r="J96" s="3">
-        <v>-412800</v>
+        <v>-410400</v>
       </c>
       <c r="K96" s="3">
         <v>-372900</v>
@@ -4163,25 +4163,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>2989800</v>
+        <v>2972400</v>
       </c>
       <c r="E100" s="3">
-        <v>2104600</v>
+        <v>2092400</v>
       </c>
       <c r="F100" s="3">
-        <v>-6592800</v>
+        <v>-6554500</v>
       </c>
       <c r="G100" s="3">
-        <v>360900</v>
+        <v>358800</v>
       </c>
       <c r="H100" s="3">
-        <v>-2411700</v>
+        <v>-2397700</v>
       </c>
       <c r="I100" s="3">
-        <v>4784900</v>
+        <v>4757100</v>
       </c>
       <c r="J100" s="3">
-        <v>-4277600</v>
+        <v>-4252800</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>5</v>
@@ -4205,25 +4205,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>38100</v>
+        <v>37900</v>
       </c>
       <c r="E101" s="3">
-        <v>-15300</v>
+        <v>-15200</v>
       </c>
       <c r="F101" s="3">
-        <v>-77700</v>
+        <v>-77200</v>
       </c>
       <c r="G101" s="3">
-        <v>25800</v>
+        <v>25600</v>
       </c>
       <c r="H101" s="3">
-        <v>-16200</v>
+        <v>-16100</v>
       </c>
       <c r="I101" s="3">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="J101" s="3">
-        <v>-12700</v>
+        <v>-12600</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>5</v>
@@ -4247,25 +4247,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-5628300</v>
+        <v>-5595700</v>
       </c>
       <c r="E102" s="3">
-        <v>4288000</v>
+        <v>4263100</v>
       </c>
       <c r="F102" s="3">
-        <v>2377900</v>
+        <v>2364100</v>
       </c>
       <c r="G102" s="3">
-        <v>4879700</v>
+        <v>4851400</v>
       </c>
       <c r="H102" s="3">
-        <v>-194000</v>
+        <v>-192800</v>
       </c>
       <c r="I102" s="3">
-        <v>1026100</v>
+        <v>1020100</v>
       </c>
       <c r="J102" s="3">
-        <v>1863900</v>
+        <v>1853000</v>
       </c>
       <c r="K102" s="3">
         <v>-75100</v>

--- a/AAII_Financials/Yearly/IBN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IBN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
   <si>
     <t>IBN</t>
   </si>
@@ -656,112 +656,118 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45016</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44651</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44286</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43921</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43555</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43190</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42825</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42460</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42094</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41729</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41364</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40999</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>14515900</v>
+        <v>19014300</v>
       </c>
       <c r="E8" s="3">
-        <v>11439300</v>
+        <v>14431200</v>
       </c>
       <c r="F8" s="3">
-        <v>10690600</v>
+        <v>11372500</v>
       </c>
       <c r="G8" s="3">
-        <v>10171800</v>
+        <v>10628200</v>
       </c>
       <c r="H8" s="3">
-        <v>8630600</v>
+        <v>10112400</v>
       </c>
       <c r="I8" s="3">
-        <v>7453300</v>
+        <v>8580200</v>
       </c>
       <c r="J8" s="3">
+        <v>7409800</v>
+      </c>
+      <c r="K8" s="3">
         <v>7306700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7168600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7101300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6798400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5933700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5494100</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -801,9 +807,12 @@
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -843,9 +852,12 @@
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,8 +874,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -903,9 +916,12 @@
       <c r="O12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,9 +961,12 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -987,51 +1006,57 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-181600</v>
+        <v>-230700</v>
       </c>
       <c r="E15" s="3">
-        <v>-159500</v>
+        <v>-180500</v>
       </c>
       <c r="F15" s="3">
-        <v>-160700</v>
+        <v>-158500</v>
       </c>
       <c r="G15" s="3">
-        <v>-140400</v>
+        <v>-159700</v>
       </c>
       <c r="H15" s="3">
-        <v>-113400</v>
+        <v>-139600</v>
       </c>
       <c r="I15" s="3">
-        <v>-110600</v>
+        <v>-112700</v>
       </c>
       <c r="J15" s="3">
+        <v>-109900</v>
+      </c>
+      <c r="K15" s="3">
         <v>-109300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-101900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-103100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-98800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-82700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-97100</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,92 +1070,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>6725400</v>
+        <v>9192200</v>
       </c>
       <c r="E17" s="3">
-        <v>5821400</v>
+        <v>6686100</v>
       </c>
       <c r="F17" s="3">
-        <v>6532300</v>
+        <v>5787400</v>
       </c>
       <c r="G17" s="3">
-        <v>6611400</v>
+        <v>6494200</v>
       </c>
       <c r="H17" s="3">
-        <v>7107700</v>
+        <v>6572800</v>
       </c>
       <c r="I17" s="3">
-        <v>6029300</v>
+        <v>7066200</v>
       </c>
       <c r="J17" s="3">
+        <v>5994100</v>
+      </c>
+      <c r="K17" s="3">
         <v>6064700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5043400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4644600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4423200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3944400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3768900</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>7790500</v>
+        <v>9822100</v>
       </c>
       <c r="E18" s="3">
-        <v>5617900</v>
+        <v>7745000</v>
       </c>
       <c r="F18" s="3">
-        <v>4158300</v>
+        <v>5585100</v>
       </c>
       <c r="G18" s="3">
-        <v>3560400</v>
+        <v>4134000</v>
       </c>
       <c r="H18" s="3">
-        <v>1522900</v>
+        <v>3539600</v>
       </c>
       <c r="I18" s="3">
-        <v>1424000</v>
+        <v>1514000</v>
       </c>
       <c r="J18" s="3">
+        <v>1415700</v>
+      </c>
+      <c r="K18" s="3">
         <v>1242000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2125200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2456700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2375200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1989300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1725200</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,77 +1179,81 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2244400</v>
+        <v>-2618300</v>
       </c>
       <c r="E20" s="3">
-        <v>-1512400</v>
+        <v>-2231300</v>
       </c>
       <c r="F20" s="3">
-        <v>-1037500</v>
+        <v>-1503500</v>
       </c>
       <c r="G20" s="3">
-        <v>-1331600</v>
+        <v>-1031400</v>
       </c>
       <c r="H20" s="3">
-        <v>-634700</v>
+        <v>-1323900</v>
       </c>
       <c r="I20" s="3">
-        <v>-107600</v>
+        <v>-630900</v>
       </c>
       <c r="J20" s="3">
+        <v>-107000</v>
+      </c>
+      <c r="K20" s="3">
         <v>413700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-395800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-88000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-138100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-189200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-179900</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5743000</v>
+        <v>7441700</v>
       </c>
       <c r="E21" s="3">
-        <v>4282500</v>
+        <v>5709900</v>
       </c>
       <c r="F21" s="3">
-        <v>3296800</v>
+        <v>4257900</v>
       </c>
       <c r="G21" s="3">
-        <v>2392600</v>
+        <v>3278000</v>
       </c>
       <c r="H21" s="3">
-        <v>1013300</v>
+        <v>2379000</v>
       </c>
       <c r="I21" s="3">
-        <v>1440600</v>
+        <v>1007700</v>
       </c>
       <c r="J21" s="3">
+        <v>1432500</v>
+      </c>
+      <c r="K21" s="3">
         <v>1780700</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1227,12 +1263,15 @@
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3">
         <v>1654500</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1272,93 +1311,102 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>5546200</v>
+        <v>7203800</v>
       </c>
       <c r="E23" s="3">
-        <v>4105500</v>
+        <v>5513800</v>
       </c>
       <c r="F23" s="3">
-        <v>3120800</v>
+        <v>4081600</v>
       </c>
       <c r="G23" s="3">
-        <v>2228800</v>
+        <v>3102600</v>
       </c>
       <c r="H23" s="3">
-        <v>888300</v>
+        <v>2215800</v>
       </c>
       <c r="I23" s="3">
-        <v>1316300</v>
+        <v>883100</v>
       </c>
       <c r="J23" s="3">
+        <v>1308600</v>
+      </c>
+      <c r="K23" s="3">
         <v>1655700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1729400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2368700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2237100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1800100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1545300</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1414000</v>
+        <v>1839000</v>
       </c>
       <c r="E24" s="3">
-        <v>1014000</v>
+        <v>1405800</v>
       </c>
       <c r="F24" s="3">
-        <v>679200</v>
+        <v>1008100</v>
       </c>
       <c r="G24" s="3">
-        <v>737400</v>
+        <v>675200</v>
       </c>
       <c r="H24" s="3">
-        <v>206100</v>
+        <v>733100</v>
       </c>
       <c r="I24" s="3">
-        <v>225300</v>
+        <v>204900</v>
       </c>
       <c r="J24" s="3">
+        <v>224000</v>
+      </c>
+      <c r="K24" s="3">
         <v>296000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>408300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>696600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>633300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>461000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>397500</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,93 +1446,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>4132100</v>
+        <v>5364800</v>
       </c>
       <c r="E26" s="3">
-        <v>3091500</v>
+        <v>4108000</v>
       </c>
       <c r="F26" s="3">
-        <v>2441600</v>
+        <v>3073400</v>
       </c>
       <c r="G26" s="3">
-        <v>1491300</v>
+        <v>2427400</v>
       </c>
       <c r="H26" s="3">
-        <v>682100</v>
+        <v>1482600</v>
       </c>
       <c r="I26" s="3">
-        <v>1091000</v>
+        <v>678100</v>
       </c>
       <c r="J26" s="3">
+        <v>1084700</v>
+      </c>
+      <c r="K26" s="3">
         <v>1359700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1321100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1672100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1603700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1339200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1147800</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>4081000</v>
+        <v>5275400</v>
       </c>
       <c r="E27" s="3">
-        <v>3010700</v>
+        <v>4057200</v>
       </c>
       <c r="F27" s="3">
-        <v>2204300</v>
+        <v>2993100</v>
       </c>
       <c r="G27" s="3">
-        <v>1292400</v>
+        <v>2191400</v>
       </c>
       <c r="H27" s="3">
-        <v>510100</v>
+        <v>1284900</v>
       </c>
       <c r="I27" s="3">
-        <v>924700</v>
+        <v>507100</v>
       </c>
       <c r="J27" s="3">
+        <v>919300</v>
+      </c>
+      <c r="K27" s="3">
         <v>1221600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1230800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1582300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1516400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1335900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1023900</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,9 +1581,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1539,11 +1599,11 @@
       <c r="F29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G29" s="3">
-        <v>-145400</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>5</v>
+      <c r="G29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H29" s="3">
+        <v>-144600</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>5</v>
@@ -1560,15 +1620,18 @@
       <c r="M29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,93 +1716,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2244400</v>
+        <v>2618300</v>
       </c>
       <c r="E32" s="3">
-        <v>1512400</v>
+        <v>2231300</v>
       </c>
       <c r="F32" s="3">
-        <v>1037500</v>
+        <v>1503500</v>
       </c>
       <c r="G32" s="3">
-        <v>1331600</v>
+        <v>1031400</v>
       </c>
       <c r="H32" s="3">
-        <v>634700</v>
+        <v>1323900</v>
       </c>
       <c r="I32" s="3">
-        <v>107600</v>
+        <v>630900</v>
       </c>
       <c r="J32" s="3">
+        <v>107000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-413700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>395800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>88000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>138100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>189200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>179900</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>4081000</v>
+        <v>5275400</v>
       </c>
       <c r="E33" s="3">
-        <v>3010700</v>
+        <v>4057200</v>
       </c>
       <c r="F33" s="3">
-        <v>2204300</v>
+        <v>2993100</v>
       </c>
       <c r="G33" s="3">
-        <v>1147000</v>
+        <v>2191400</v>
       </c>
       <c r="H33" s="3">
-        <v>510100</v>
+        <v>1140300</v>
       </c>
       <c r="I33" s="3">
-        <v>924700</v>
+        <v>507100</v>
       </c>
       <c r="J33" s="3">
+        <v>919300</v>
+      </c>
+      <c r="K33" s="3">
         <v>1221600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1230800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1582300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1516400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1335900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1023900</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,98 +1851,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>4081000</v>
+        <v>5275400</v>
       </c>
       <c r="E35" s="3">
-        <v>3010700</v>
+        <v>4057200</v>
       </c>
       <c r="F35" s="3">
-        <v>2204300</v>
+        <v>2993100</v>
       </c>
       <c r="G35" s="3">
-        <v>1147000</v>
+        <v>2191400</v>
       </c>
       <c r="H35" s="3">
-        <v>510100</v>
+        <v>1140300</v>
       </c>
       <c r="I35" s="3">
-        <v>924700</v>
+        <v>507100</v>
       </c>
       <c r="J35" s="3">
+        <v>919300</v>
+      </c>
+      <c r="K35" s="3">
         <v>1221600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1230800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1582300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1516400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1335900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1023900</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45016</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44651</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44286</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43921</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43555</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43190</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42825</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42460</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42094</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41729</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41364</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40999</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,92 +1987,99 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>13789400</v>
+        <v>16194600</v>
       </c>
       <c r="E41" s="3">
-        <v>14177600</v>
+        <v>13708900</v>
       </c>
       <c r="F41" s="3">
-        <v>12420500</v>
+        <v>14094900</v>
       </c>
       <c r="G41" s="3">
-        <v>6089600</v>
+        <v>12348000</v>
       </c>
       <c r="H41" s="3">
-        <v>6876900</v>
+        <v>6054000</v>
       </c>
       <c r="I41" s="3">
-        <v>6680400</v>
+        <v>6836800</v>
       </c>
       <c r="J41" s="3">
+        <v>6641400</v>
+      </c>
+      <c r="K41" s="3">
         <v>6957800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6136300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5980200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5999100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2554200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2997300</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>31291800</v>
+        <v>30110300</v>
       </c>
       <c r="E42" s="3">
-        <v>35252000</v>
+        <v>24835400</v>
       </c>
       <c r="F42" s="3">
-        <v>33527700</v>
+        <v>30087600</v>
       </c>
       <c r="G42" s="3">
-        <v>32828700</v>
+        <v>27334100</v>
       </c>
       <c r="H42" s="3">
-        <v>28524000</v>
+        <v>27977900</v>
       </c>
       <c r="I42" s="3">
-        <v>26723400</v>
+        <v>23691500</v>
       </c>
       <c r="J42" s="3">
+        <v>22519000</v>
+      </c>
+      <c r="K42" s="3">
         <v>27788600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>18542900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>22171000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>22326800</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2027,9 +2119,12 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2069,9 +2164,12 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2111,9 +2209,12 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2153,39 +2254,42 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>240300</v>
+        <v>180000</v>
       </c>
       <c r="E47" s="3">
-        <v>240300</v>
+        <v>238900</v>
       </c>
       <c r="F47" s="3">
-        <v>80600</v>
+        <v>238900</v>
       </c>
       <c r="G47" s="3">
-        <v>83600</v>
+        <v>80200</v>
       </c>
       <c r="H47" s="3">
-        <v>87400</v>
+        <v>83100</v>
       </c>
       <c r="I47" s="3">
-        <v>59700</v>
+        <v>86900</v>
       </c>
       <c r="J47" s="3">
+        <v>59400</v>
+      </c>
+      <c r="K47" s="3">
         <v>45100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>44700</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>5</v>
       </c>
@@ -2195,93 +2299,102 @@
       <c r="O47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1315200</v>
+        <v>1578200</v>
       </c>
       <c r="E48" s="3">
-        <v>1271600</v>
+        <v>1307500</v>
       </c>
       <c r="F48" s="3">
-        <v>1296000</v>
+        <v>1264200</v>
       </c>
       <c r="G48" s="3">
-        <v>1248000</v>
+        <v>1288500</v>
       </c>
       <c r="H48" s="3">
-        <v>1158300</v>
+        <v>1240700</v>
       </c>
       <c r="I48" s="3">
-        <v>1134900</v>
+        <v>1151500</v>
       </c>
       <c r="J48" s="3">
+        <v>1128200</v>
+      </c>
+      <c r="K48" s="3">
         <v>1119600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1053500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>758600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>756600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>724100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>785500</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>294900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>12100</v>
+      </c>
+      <c r="F49" s="3">
+        <v>14700</v>
+      </c>
+      <c r="G49" s="3">
         <v>14800</v>
       </c>
-      <c r="E49" s="3">
-        <v>14800</v>
-      </c>
-      <c r="F49" s="3">
-        <v>14900</v>
-      </c>
-      <c r="G49" s="3">
-        <v>15100</v>
-      </c>
       <c r="H49" s="3">
-        <v>15100</v>
+        <v>15000</v>
       </c>
       <c r="I49" s="3">
-        <v>14100</v>
+        <v>15000</v>
       </c>
       <c r="J49" s="3">
+        <v>14000</v>
+      </c>
+      <c r="K49" s="3">
         <v>14200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>15200</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>19700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>18900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>20700</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,51 +2479,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>913600</v>
+        <v>752300</v>
       </c>
       <c r="E52" s="3">
-        <v>953000</v>
+        <v>908200</v>
       </c>
       <c r="F52" s="3">
-        <v>1119300</v>
+        <v>947500</v>
       </c>
       <c r="G52" s="3">
-        <v>1056000</v>
+        <v>1112700</v>
       </c>
       <c r="H52" s="3">
-        <v>1311400</v>
+        <v>1049800</v>
       </c>
       <c r="I52" s="3">
-        <v>937400</v>
+        <v>1303700</v>
       </c>
       <c r="J52" s="3">
+        <v>931900</v>
+      </c>
+      <c r="K52" s="3">
         <v>1346000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>599800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>208500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>127800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>354600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>405400</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,51 +2569,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>234823000</v>
+        <v>281796000</v>
       </c>
       <c r="E54" s="3">
-        <v>210141000</v>
+        <v>233452000</v>
       </c>
       <c r="F54" s="3">
-        <v>188700000</v>
+        <v>208914000</v>
       </c>
       <c r="G54" s="3">
-        <v>165137000</v>
+        <v>187598000</v>
       </c>
       <c r="H54" s="3">
-        <v>148531000</v>
+        <v>164173000</v>
       </c>
       <c r="I54" s="3">
-        <v>134801000</v>
+        <v>147664000</v>
       </c>
       <c r="J54" s="3">
+        <v>134014000</v>
+      </c>
+      <c r="K54" s="3">
         <v>118188000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>111078000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>106729000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>102743000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>89278900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>89548900</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,50 +2655,54 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3311900</v>
+        <v>8083000</v>
       </c>
       <c r="E57" s="3">
-        <v>2806000</v>
+        <v>3292600</v>
       </c>
       <c r="F57" s="3">
-        <v>4712200</v>
+        <v>2789600</v>
       </c>
       <c r="G57" s="3">
-        <v>4570600</v>
+        <v>4684700</v>
       </c>
       <c r="H57" s="3">
-        <v>4479500</v>
+        <v>4544000</v>
       </c>
       <c r="I57" s="3">
-        <v>3779500</v>
+        <v>4453300</v>
       </c>
       <c r="J57" s="3">
+        <v>3757500</v>
+      </c>
+      <c r="K57" s="3">
         <v>3179300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2412900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2288200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2637600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2609300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2105500</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2609,9 +2742,12 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2624,36 +2760,39 @@
       <c r="F59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G59" s="3">
-        <v>0</v>
+      <c r="G59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
         <v>1500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>397300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>422500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>407000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>349000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>311500</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2693,93 +2832,102 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>21493200</v>
+        <v>22663700</v>
       </c>
       <c r="E61" s="3">
-        <v>18292800</v>
+        <v>21367700</v>
       </c>
       <c r="F61" s="3">
-        <v>16747800</v>
+        <v>18186000</v>
       </c>
       <c r="G61" s="3">
-        <v>25252700</v>
+        <v>16650000</v>
       </c>
       <c r="H61" s="3">
-        <v>24988900</v>
+        <v>25105300</v>
       </c>
       <c r="I61" s="3">
-        <v>27350600</v>
+        <v>24843000</v>
       </c>
       <c r="J61" s="3">
+        <v>27190900</v>
+      </c>
+      <c r="K61" s="3">
         <v>22430800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>26538500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>27293800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>25218700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>22873100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>23323500</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>598900</v>
+        <v>2412600</v>
       </c>
       <c r="E62" s="3">
-        <v>534600</v>
+        <v>2335100</v>
       </c>
       <c r="F62" s="3">
-        <v>1376400</v>
+        <v>531500</v>
       </c>
       <c r="G62" s="3">
-        <v>794200</v>
+        <v>1368300</v>
       </c>
       <c r="H62" s="3">
-        <v>377600</v>
+        <v>789500</v>
       </c>
       <c r="I62" s="3">
-        <v>342600</v>
+        <v>375400</v>
       </c>
       <c r="J62" s="3">
+        <v>340600</v>
+      </c>
+      <c r="K62" s="3">
         <v>306000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>352800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>329600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>294600</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,51 +3057,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>209105000</v>
+        <v>251264000</v>
       </c>
       <c r="E66" s="3">
-        <v>188313000</v>
+        <v>207884000</v>
       </c>
       <c r="F66" s="3">
-        <v>169805000</v>
+        <v>187214000</v>
       </c>
       <c r="G66" s="3">
-        <v>150394000</v>
+        <v>168814000</v>
       </c>
       <c r="H66" s="3">
-        <v>134832000</v>
+        <v>149516000</v>
       </c>
       <c r="I66" s="3">
-        <v>121537000</v>
+        <v>134045000</v>
       </c>
       <c r="J66" s="3">
+        <v>120827000</v>
+      </c>
+      <c r="K66" s="3">
         <v>105643000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>99699600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>95785600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>92241100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>80181600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>80688300</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,51 +3301,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>18563600</v>
+        <v>23020800</v>
       </c>
       <c r="E72" s="3">
-        <v>14882500</v>
+        <v>18455200</v>
       </c>
       <c r="F72" s="3">
-        <v>12116300</v>
+        <v>14795600</v>
       </c>
       <c r="G72" s="3">
-        <v>9712300</v>
+        <v>12045600</v>
       </c>
       <c r="H72" s="3">
-        <v>8845600</v>
+        <v>9655600</v>
       </c>
       <c r="I72" s="3">
-        <v>8594000</v>
+        <v>8794000</v>
       </c>
       <c r="J72" s="3">
+        <v>8543800</v>
+      </c>
+      <c r="K72" s="3">
         <v>7922300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6759100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6373200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5639000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4568300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4003000</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,51 +3481,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>25718300</v>
+        <v>30532300</v>
       </c>
       <c r="E76" s="3">
-        <v>21828100</v>
+        <v>25568100</v>
       </c>
       <c r="F76" s="3">
-        <v>18894700</v>
+        <v>21700700</v>
       </c>
       <c r="G76" s="3">
-        <v>14742900</v>
+        <v>18784400</v>
       </c>
       <c r="H76" s="3">
-        <v>13699000</v>
+        <v>14656800</v>
       </c>
       <c r="I76" s="3">
-        <v>13264500</v>
+        <v>13619000</v>
       </c>
       <c r="J76" s="3">
+        <v>13187100</v>
+      </c>
+      <c r="K76" s="3">
         <v>12545400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11378000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10943800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10501500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9097300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8860600</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,98 +3571,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45016</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44651</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44286</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43921</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43555</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43190</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42825</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42460</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42094</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41729</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41364</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40999</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>4081000</v>
+        <v>5275400</v>
       </c>
       <c r="E81" s="3">
-        <v>3010700</v>
+        <v>4057200</v>
       </c>
       <c r="F81" s="3">
-        <v>2204300</v>
+        <v>2993100</v>
       </c>
       <c r="G81" s="3">
-        <v>1147000</v>
+        <v>2191400</v>
       </c>
       <c r="H81" s="3">
-        <v>510100</v>
+        <v>1140300</v>
       </c>
       <c r="I81" s="3">
-        <v>924700</v>
+        <v>507100</v>
       </c>
       <c r="J81" s="3">
+        <v>919300</v>
+      </c>
+      <c r="K81" s="3">
         <v>1221600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1230800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1582300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1516400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1335900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1023900</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,35 +3688,36 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>197300</v>
+        <v>237900</v>
       </c>
       <c r="E83" s="3">
-        <v>177400</v>
+        <v>196200</v>
       </c>
       <c r="F83" s="3">
         <v>176400</v>
       </c>
       <c r="G83" s="3">
-        <v>164200</v>
+        <v>175400</v>
       </c>
       <c r="H83" s="3">
-        <v>125300</v>
+        <v>163300</v>
       </c>
       <c r="I83" s="3">
         <v>124600</v>
       </c>
       <c r="J83" s="3">
+        <v>123900</v>
+      </c>
+      <c r="K83" s="3">
         <v>125200</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>5</v>
       </c>
@@ -3529,12 +3727,15 @@
       <c r="N83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
         <v>109100</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,51 +3955,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-452200</v>
+        <v>18840200</v>
       </c>
       <c r="E89" s="3">
-        <v>6900600</v>
+        <v>-449500</v>
       </c>
       <c r="F89" s="3">
-        <v>16548000</v>
+        <v>6860300</v>
       </c>
       <c r="G89" s="3">
-        <v>9539800</v>
+        <v>16451400</v>
       </c>
       <c r="H89" s="3">
-        <v>5835700</v>
+        <v>9484100</v>
       </c>
       <c r="I89" s="3">
-        <v>2324000</v>
+        <v>5801600</v>
       </c>
       <c r="J89" s="3">
+        <v>2310400</v>
+      </c>
+      <c r="K89" s="3">
         <v>6311000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1483800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>874000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>929500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2312700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-985300</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,50 +4022,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-295900</v>
+        <v>-438500</v>
       </c>
       <c r="E91" s="3">
-        <v>-223000</v>
+        <v>-294100</v>
       </c>
       <c r="F91" s="3">
-        <v>-202400</v>
+        <v>-221700</v>
       </c>
       <c r="G91" s="3">
-        <v>-224600</v>
+        <v>-201200</v>
       </c>
       <c r="H91" s="3">
-        <v>-137700</v>
+        <v>-223300</v>
       </c>
       <c r="I91" s="3">
-        <v>-125000</v>
+        <v>-136900</v>
       </c>
       <c r="J91" s="3">
+        <v>-124200</v>
+      </c>
+      <c r="K91" s="3">
         <v>-157900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-150500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-108200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-115100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-82600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-87500</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,36 +4154,39 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-8153800</v>
+        <v>-17395000</v>
       </c>
       <c r="E94" s="3">
-        <v>-4714600</v>
+        <v>-8106200</v>
       </c>
       <c r="F94" s="3">
-        <v>-7552100</v>
+        <v>-4687100</v>
       </c>
       <c r="G94" s="3">
-        <v>-5072800</v>
+        <v>-7508000</v>
       </c>
       <c r="H94" s="3">
-        <v>-3614700</v>
+        <v>-5043200</v>
       </c>
       <c r="I94" s="3">
-        <v>-6063800</v>
+        <v>-3593500</v>
       </c>
       <c r="J94" s="3">
+        <v>-6028400</v>
+      </c>
+      <c r="K94" s="3">
         <v>-192500</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>5</v>
       </c>
@@ -3967,12 +4196,15 @@
       <c r="N94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
         <v>-3074600</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,50 +4221,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-417200</v>
+        <v>-667400</v>
       </c>
       <c r="E96" s="3">
-        <v>-166100</v>
+        <v>-414700</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-165100</v>
       </c>
       <c r="G96" s="3">
-        <v>-106300</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-140100</v>
+        <v>-105700</v>
       </c>
       <c r="I96" s="3">
-        <v>-205800</v>
+        <v>-139300</v>
       </c>
       <c r="J96" s="3">
+        <v>-204600</v>
+      </c>
+      <c r="K96" s="3">
         <v>-410400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-372900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-349400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-371500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-293400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-274900</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,36 +4398,39 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>2972400</v>
+        <v>1640700</v>
       </c>
       <c r="E100" s="3">
-        <v>2092400</v>
+        <v>2955100</v>
       </c>
       <c r="F100" s="3">
-        <v>-6554500</v>
+        <v>2080200</v>
       </c>
       <c r="G100" s="3">
-        <v>358800</v>
+        <v>-6516300</v>
       </c>
       <c r="H100" s="3">
-        <v>-2397700</v>
+        <v>356700</v>
       </c>
       <c r="I100" s="3">
-        <v>4757100</v>
+        <v>-2383700</v>
       </c>
       <c r="J100" s="3">
+        <v>4729400</v>
+      </c>
+      <c r="K100" s="3">
         <v>-4252800</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>5</v>
       </c>
@@ -4195,39 +4440,42 @@
       <c r="N100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
         <v>4256900</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>37900</v>
+        <v>50500</v>
       </c>
       <c r="E101" s="3">
-        <v>-15200</v>
+        <v>37700</v>
       </c>
       <c r="F101" s="3">
-        <v>-77200</v>
+        <v>-15100</v>
       </c>
       <c r="G101" s="3">
-        <v>25600</v>
+        <v>-76800</v>
       </c>
       <c r="H101" s="3">
-        <v>-16100</v>
+        <v>25500</v>
       </c>
       <c r="I101" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="J101" s="3">
         <v>2700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-12600</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
@@ -4237,52 +4485,58 @@
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
         <v>59100</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-5595700</v>
+        <v>3136400</v>
       </c>
       <c r="E102" s="3">
-        <v>4263100</v>
+        <v>-5563000</v>
       </c>
       <c r="F102" s="3">
-        <v>2364100</v>
+        <v>4238200</v>
       </c>
       <c r="G102" s="3">
-        <v>4851400</v>
+        <v>2350300</v>
       </c>
       <c r="H102" s="3">
-        <v>-192800</v>
+        <v>4823100</v>
       </c>
       <c r="I102" s="3">
-        <v>1020100</v>
+        <v>-191700</v>
       </c>
       <c r="J102" s="3">
+        <v>1014200</v>
+      </c>
+      <c r="K102" s="3">
         <v>1853000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-75100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-143800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-152900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1086000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>256100</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/IBN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IBN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
   <si>
     <t>IBN</t>
   </si>
@@ -727,25 +727,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>19014300</v>
+        <v>17137800</v>
       </c>
       <c r="E8" s="3">
-        <v>14431200</v>
+        <v>14235400</v>
       </c>
       <c r="F8" s="3">
-        <v>11372500</v>
+        <v>13036700</v>
       </c>
       <c r="G8" s="3">
-        <v>10628200</v>
+        <v>13189100</v>
       </c>
       <c r="H8" s="3">
-        <v>10112400</v>
+        <v>10965300</v>
       </c>
       <c r="I8" s="3">
-        <v>8580200</v>
+        <v>10343800</v>
       </c>
       <c r="J8" s="3">
-        <v>7409800</v>
+        <v>10255000</v>
       </c>
       <c r="K8" s="3">
         <v>7306700</v>
@@ -816,26 +816,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>17137800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>14235400</v>
+      </c>
+      <c r="F10" s="3">
+        <v>13036700</v>
+      </c>
+      <c r="G10" s="3">
+        <v>13189100</v>
+      </c>
+      <c r="H10" s="3">
+        <v>10965300</v>
+      </c>
+      <c r="I10" s="3">
+        <v>10343800</v>
+      </c>
+      <c r="J10" s="3">
+        <v>10255000</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -970,26 +970,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1016,25 +1016,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-230700</v>
+        <v>229800</v>
       </c>
       <c r="E15" s="3">
-        <v>-180500</v>
+        <v>189900</v>
       </c>
       <c r="F15" s="3">
-        <v>-158500</v>
+        <v>193700</v>
       </c>
       <c r="G15" s="3">
-        <v>-159700</v>
+        <v>201100</v>
       </c>
       <c r="H15" s="3">
-        <v>-139600</v>
+        <v>181900</v>
       </c>
       <c r="I15" s="3">
-        <v>-112700</v>
+        <v>150900</v>
       </c>
       <c r="J15" s="3">
-        <v>-109900</v>
+        <v>159700</v>
       </c>
       <c r="K15" s="3">
         <v>-109300</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>9192200</v>
+        <v>11736000</v>
       </c>
       <c r="E17" s="3">
-        <v>6686100</v>
+        <v>10038800</v>
       </c>
       <c r="F17" s="3">
-        <v>5787400</v>
+        <v>9639200</v>
       </c>
       <c r="G17" s="3">
-        <v>6494200</v>
+        <v>10425300</v>
       </c>
       <c r="H17" s="3">
-        <v>6572800</v>
+        <v>9497800</v>
       </c>
       <c r="I17" s="3">
-        <v>7066200</v>
+        <v>9274600</v>
       </c>
       <c r="J17" s="3">
-        <v>5994100</v>
+        <v>8567900</v>
       </c>
       <c r="K17" s="3">
         <v>6064700</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>9822100</v>
+        <v>5401800</v>
       </c>
       <c r="E18" s="3">
-        <v>7745000</v>
+        <v>4196600</v>
       </c>
       <c r="F18" s="3">
-        <v>5585100</v>
+        <v>3397500</v>
       </c>
       <c r="G18" s="3">
-        <v>4134000</v>
+        <v>2763800</v>
       </c>
       <c r="H18" s="3">
-        <v>3539600</v>
+        <v>1467500</v>
       </c>
       <c r="I18" s="3">
-        <v>1514000</v>
+        <v>1069200</v>
       </c>
       <c r="J18" s="3">
-        <v>1415700</v>
+        <v>1687000</v>
       </c>
       <c r="K18" s="3">
         <v>1242000</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2618300</v>
+        <v>-128900</v>
       </c>
       <c r="E20" s="3">
-        <v>-2231300</v>
+        <v>-121600</v>
       </c>
       <c r="F20" s="3">
-        <v>-1503500</v>
+        <v>-99400</v>
       </c>
       <c r="G20" s="3">
-        <v>-1031400</v>
+        <v>-19700</v>
       </c>
       <c r="H20" s="3">
-        <v>-1323900</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-630900</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-107000</v>
+        <v>-23300</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K20" s="3">
         <v>413700</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>7441700</v>
+        <v>5760400</v>
       </c>
       <c r="E21" s="3">
-        <v>5709900</v>
+        <v>4508100</v>
       </c>
       <c r="F21" s="3">
-        <v>4257900</v>
+        <v>3690600</v>
       </c>
       <c r="G21" s="3">
-        <v>3278000</v>
+        <v>2984600</v>
       </c>
       <c r="H21" s="3">
-        <v>2379000</v>
+        <v>1672700</v>
       </c>
       <c r="I21" s="3">
-        <v>1007700</v>
+        <v>1220100</v>
       </c>
       <c r="J21" s="3">
-        <v>1432500</v>
+        <v>1846700</v>
       </c>
       <c r="K21" s="3">
         <v>1780700</v>
@@ -1275,26 +1275,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1321,25 +1321,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>7203800</v>
+        <v>5530600</v>
       </c>
       <c r="E23" s="3">
-        <v>5513800</v>
+        <v>4318200</v>
       </c>
       <c r="F23" s="3">
-        <v>4081600</v>
+        <v>3496900</v>
       </c>
       <c r="G23" s="3">
-        <v>3102600</v>
+        <v>2783500</v>
       </c>
       <c r="H23" s="3">
-        <v>2215800</v>
+        <v>1490800</v>
       </c>
       <c r="I23" s="3">
-        <v>883100</v>
+        <v>1069200</v>
       </c>
       <c r="J23" s="3">
-        <v>1308600</v>
+        <v>1687000</v>
       </c>
       <c r="K23" s="3">
         <v>1655700</v>
@@ -1365,26 +1365,26 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>1839000</v>
-      </c>
-      <c r="E24" s="3">
-        <v>1405800</v>
-      </c>
-      <c r="F24" s="3">
-        <v>1008100</v>
-      </c>
-      <c r="G24" s="3">
-        <v>675200</v>
-      </c>
-      <c r="H24" s="3">
-        <v>733100</v>
+      <c r="D24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I24" s="3">
-        <v>204900</v>
+        <v>248100</v>
       </c>
       <c r="J24" s="3">
-        <v>224000</v>
+        <v>288700</v>
       </c>
       <c r="K24" s="3">
         <v>296000</v>
@@ -1456,25 +1456,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>5364800</v>
+        <v>5530600</v>
       </c>
       <c r="E26" s="3">
-        <v>4108000</v>
+        <v>4318200</v>
       </c>
       <c r="F26" s="3">
-        <v>3073400</v>
+        <v>3496900</v>
       </c>
       <c r="G26" s="3">
-        <v>2427400</v>
+        <v>2783500</v>
       </c>
       <c r="H26" s="3">
-        <v>1482600</v>
+        <v>1490800</v>
       </c>
       <c r="I26" s="3">
-        <v>678100</v>
+        <v>821100</v>
       </c>
       <c r="J26" s="3">
-        <v>1084700</v>
+        <v>1398300</v>
       </c>
       <c r="K26" s="3">
         <v>1359700</v>
@@ -1501,25 +1501,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>5275400</v>
+        <v>5311700</v>
       </c>
       <c r="E27" s="3">
-        <v>4057200</v>
+        <v>4144700</v>
       </c>
       <c r="F27" s="3">
-        <v>2993100</v>
+        <v>3308800</v>
       </c>
       <c r="G27" s="3">
-        <v>2191400</v>
+        <v>2512900</v>
       </c>
       <c r="H27" s="3">
-        <v>1284900</v>
+        <v>1270400</v>
       </c>
       <c r="I27" s="3">
-        <v>507100</v>
+        <v>614000</v>
       </c>
       <c r="J27" s="3">
-        <v>919300</v>
+        <v>1185100</v>
       </c>
       <c r="K27" s="3">
         <v>1221600</v>
@@ -1590,26 +1590,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>5</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>-144600</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>5</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2618300</v>
+        <v>128900</v>
       </c>
       <c r="E32" s="3">
-        <v>2231300</v>
+        <v>121600</v>
       </c>
       <c r="F32" s="3">
-        <v>1503500</v>
+        <v>99400</v>
       </c>
       <c r="G32" s="3">
-        <v>1031400</v>
+        <v>19700</v>
       </c>
       <c r="H32" s="3">
-        <v>1323900</v>
-      </c>
-      <c r="I32" s="3">
-        <v>630900</v>
-      </c>
-      <c r="J32" s="3">
-        <v>107000</v>
+        <v>23300</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K32" s="3">
         <v>-413700</v>
@@ -1771,25 +1771,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>5275400</v>
+        <v>5311700</v>
       </c>
       <c r="E33" s="3">
-        <v>4057200</v>
+        <v>4144700</v>
       </c>
       <c r="F33" s="3">
-        <v>2993100</v>
+        <v>3308800</v>
       </c>
       <c r="G33" s="3">
-        <v>2191400</v>
+        <v>2512900</v>
       </c>
       <c r="H33" s="3">
-        <v>1140300</v>
+        <v>1270400</v>
       </c>
       <c r="I33" s="3">
-        <v>507100</v>
+        <v>614000</v>
       </c>
       <c r="J33" s="3">
-        <v>919300</v>
+        <v>1185100</v>
       </c>
       <c r="K33" s="3">
         <v>1221600</v>
@@ -1861,25 +1861,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>5275400</v>
+        <v>5311700</v>
       </c>
       <c r="E35" s="3">
-        <v>4057200</v>
+        <v>4144700</v>
       </c>
       <c r="F35" s="3">
-        <v>2993100</v>
+        <v>3308800</v>
       </c>
       <c r="G35" s="3">
-        <v>2191400</v>
+        <v>2512900</v>
       </c>
       <c r="H35" s="3">
-        <v>1140300</v>
+        <v>1270400</v>
       </c>
       <c r="I35" s="3">
-        <v>507100</v>
+        <v>614000</v>
       </c>
       <c r="J35" s="3">
-        <v>919300</v>
+        <v>1185100</v>
       </c>
       <c r="K35" s="3">
         <v>1221600</v>
@@ -1994,25 +1994,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>16194600</v>
+        <v>9815500</v>
       </c>
       <c r="E41" s="3">
-        <v>13708900</v>
+        <v>9314200</v>
       </c>
       <c r="F41" s="3">
-        <v>14094900</v>
+        <v>10636800</v>
       </c>
       <c r="G41" s="3">
-        <v>12348000</v>
+        <v>14818200</v>
       </c>
       <c r="H41" s="3">
-        <v>6054000</v>
+        <v>13613700</v>
       </c>
       <c r="I41" s="3">
-        <v>6836800</v>
+        <v>8405300</v>
       </c>
       <c r="J41" s="3">
-        <v>6641400</v>
+        <v>9825300</v>
       </c>
       <c r="K41" s="3">
         <v>6957800</v>
@@ -2039,25 +2039,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>30110300</v>
+        <v>2040200</v>
       </c>
       <c r="E42" s="3">
-        <v>24835400</v>
+        <v>2167800</v>
       </c>
       <c r="F42" s="3">
-        <v>30087600</v>
+        <v>1388200</v>
       </c>
       <c r="G42" s="3">
-        <v>27334100</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>27977900</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>23691500</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>22519000</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>27788600</v>
@@ -2083,26 +2083,26 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>61300</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2128,26 +2128,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I44" s="3">
-        <v>0</v>
+        <v>144900</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>303500</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2174,25 +2174,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>3526600</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>2756500</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>2302400</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>2582000</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>2882300</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>3134000</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>2673500</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2219,25 +2219,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>25102600</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>21540900</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>27821100</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>22752900</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>19861500</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>15892100</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>16714600</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2264,25 +2264,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>180000</v>
+        <v>79492500</v>
       </c>
       <c r="E47" s="3">
-        <v>238900</v>
+        <v>60337200</v>
       </c>
       <c r="F47" s="3">
-        <v>238900</v>
+        <v>54846800</v>
       </c>
       <c r="G47" s="3">
-        <v>80200</v>
+        <v>54405300</v>
       </c>
       <c r="H47" s="3">
-        <v>83100</v>
+        <v>46001100</v>
       </c>
       <c r="I47" s="3">
-        <v>86900</v>
+        <v>41459900</v>
       </c>
       <c r="J47" s="3">
-        <v>59400</v>
+        <v>42213700</v>
       </c>
       <c r="K47" s="3">
         <v>45100</v>
@@ -2309,25 +2309,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1578200</v>
+        <v>1589100</v>
       </c>
       <c r="E48" s="3">
-        <v>1307500</v>
+        <v>1335700</v>
       </c>
       <c r="F48" s="3">
-        <v>1264200</v>
+        <v>1397500</v>
       </c>
       <c r="G48" s="3">
-        <v>1288500</v>
+        <v>1477500</v>
       </c>
       <c r="H48" s="3">
-        <v>1240700</v>
+        <v>1382300</v>
       </c>
       <c r="I48" s="3">
-        <v>1151500</v>
+        <v>1394300</v>
       </c>
       <c r="J48" s="3">
-        <v>1128200</v>
+        <v>1454500</v>
       </c>
       <c r="K48" s="3">
         <v>1119600</v>
@@ -2354,25 +2354,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>294900</v>
+        <v>297000</v>
       </c>
       <c r="E49" s="3">
-        <v>12100</v>
+        <v>12300</v>
       </c>
       <c r="F49" s="3">
+        <v>13400</v>
+      </c>
+      <c r="G49" s="3">
         <v>14700</v>
       </c>
-      <c r="G49" s="3">
-        <v>14800</v>
-      </c>
       <c r="H49" s="3">
-        <v>15000</v>
+        <v>14600</v>
       </c>
       <c r="I49" s="3">
-        <v>15000</v>
+        <v>15800</v>
       </c>
       <c r="J49" s="3">
-        <v>14000</v>
+        <v>17200</v>
       </c>
       <c r="K49" s="3">
         <v>14200</v>
@@ -2489,25 +2489,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>752300</v>
+        <v>25179200</v>
       </c>
       <c r="E52" s="3">
-        <v>908200</v>
+        <v>22350600</v>
       </c>
       <c r="F52" s="3">
-        <v>947500</v>
+        <v>24549900</v>
       </c>
       <c r="G52" s="3">
-        <v>1112700</v>
+        <v>26964000</v>
       </c>
       <c r="H52" s="3">
-        <v>1049800</v>
+        <v>20687500</v>
       </c>
       <c r="I52" s="3">
-        <v>1303700</v>
+        <v>25079200</v>
       </c>
       <c r="J52" s="3">
-        <v>931900</v>
+        <v>24057700</v>
       </c>
       <c r="K52" s="3">
         <v>1346000</v>
@@ -2579,25 +2579,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>281796000</v>
+        <v>283737700</v>
       </c>
       <c r="E54" s="3">
-        <v>233452000</v>
+        <v>238489000</v>
       </c>
       <c r="F54" s="3">
-        <v>208914000</v>
+        <v>230945100</v>
       </c>
       <c r="G54" s="3">
-        <v>187598000</v>
+        <v>215118900</v>
       </c>
       <c r="H54" s="3">
-        <v>164173000</v>
+        <v>182907800</v>
       </c>
       <c r="I54" s="3">
-        <v>147664000</v>
+        <v>178796800</v>
       </c>
       <c r="J54" s="3">
-        <v>134014000</v>
+        <v>172767000</v>
       </c>
       <c r="K54" s="3">
         <v>118188000</v>
@@ -2662,25 +2662,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>8083000</v>
+        <v>180931000</v>
       </c>
       <c r="E57" s="3">
-        <v>3292600</v>
+        <v>150402200</v>
       </c>
       <c r="F57" s="3">
-        <v>2789600</v>
+        <v>146530400</v>
       </c>
       <c r="G57" s="3">
-        <v>4684700</v>
+        <v>136243400</v>
       </c>
       <c r="H57" s="3">
-        <v>4544000</v>
+        <v>111000800</v>
       </c>
       <c r="I57" s="3">
-        <v>4453300</v>
+        <v>103198700</v>
       </c>
       <c r="J57" s="3">
-        <v>3757500</v>
+        <v>94311000</v>
       </c>
       <c r="K57" s="3">
         <v>3179300</v>
@@ -2707,25 +2707,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>14551100</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>12577700</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>1192900</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>578600</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>430700</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>275600</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>198300</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2751,26 +2751,26 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>5</v>
+      <c r="D59" s="3">
+        <v>1543600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1695900</v>
+      </c>
+      <c r="F59" s="3">
+        <v>1780300</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1800800</v>
       </c>
       <c r="H59" s="3">
-        <v>0</v>
+        <v>857700</v>
       </c>
       <c r="I59" s="3">
-        <v>1500</v>
+        <v>1256200</v>
       </c>
       <c r="J59" s="3">
-        <v>4600</v>
+        <v>1143700</v>
       </c>
       <c r="K59" s="3">
         <v>9500</v>
@@ -2797,25 +2797,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>197493700</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>165082400</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>149866300</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>138962100</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>112697000</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>105259500</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>96204600</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2842,25 +2842,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>22663700</v>
+        <v>12469600</v>
       </c>
       <c r="E61" s="3">
-        <v>21367700</v>
+        <v>12691300</v>
       </c>
       <c r="F61" s="3">
-        <v>18186000</v>
+        <v>21601200</v>
       </c>
       <c r="G61" s="3">
-        <v>16650000</v>
+        <v>19102800</v>
       </c>
       <c r="H61" s="3">
-        <v>25105300</v>
+        <v>27973700</v>
       </c>
       <c r="I61" s="3">
-        <v>24843000</v>
+        <v>30080800</v>
       </c>
       <c r="J61" s="3">
-        <v>27190900</v>
+        <v>35053700</v>
       </c>
       <c r="K61" s="3">
         <v>22430800</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2412600</v>
+        <v>41364900</v>
       </c>
       <c r="E62" s="3">
-        <v>2335100</v>
+        <v>33781200</v>
       </c>
       <c r="F62" s="3">
-        <v>531500</v>
+        <v>34700400</v>
       </c>
       <c r="G62" s="3">
-        <v>1368300</v>
+        <v>34203300</v>
       </c>
       <c r="H62" s="3">
-        <v>789500</v>
+        <v>25005400</v>
       </c>
       <c r="I62" s="3">
-        <v>375400</v>
+        <v>26016500</v>
       </c>
       <c r="J62" s="3">
-        <v>340600</v>
+        <v>23585100</v>
       </c>
       <c r="K62" s="3">
         <v>306000</v>
@@ -3067,25 +3067,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>251264000</v>
+        <v>251328100</v>
       </c>
       <c r="E66" s="3">
-        <v>207884000</v>
+        <v>211554900</v>
       </c>
       <c r="F66" s="3">
-        <v>187214000</v>
+        <v>206167900</v>
       </c>
       <c r="G66" s="3">
-        <v>168814000</v>
+        <v>192268200</v>
       </c>
       <c r="H66" s="3">
-        <v>149516000</v>
+        <v>165676100</v>
       </c>
       <c r="I66" s="3">
-        <v>134045000</v>
+        <v>161356700</v>
       </c>
       <c r="J66" s="3">
-        <v>120827000</v>
+        <v>154843400</v>
       </c>
       <c r="K66" s="3">
         <v>105643000</v>
@@ -3311,25 +3311,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>23020800</v>
+        <v>21618800</v>
       </c>
       <c r="E72" s="3">
-        <v>18455200</v>
+        <v>17217300</v>
       </c>
       <c r="F72" s="3">
-        <v>14795600</v>
+        <v>14606300</v>
       </c>
       <c r="G72" s="3">
-        <v>12045600</v>
+        <v>12156700</v>
       </c>
       <c r="H72" s="3">
-        <v>9655600</v>
+        <v>9235900</v>
       </c>
       <c r="I72" s="3">
-        <v>8794000</v>
+        <v>8927700</v>
       </c>
       <c r="J72" s="3">
-        <v>8543800</v>
+        <v>9047000</v>
       </c>
       <c r="K72" s="3">
         <v>7922300</v>
@@ -3491,25 +3491,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>30532300</v>
+        <v>30742700</v>
       </c>
       <c r="E76" s="3">
-        <v>25568100</v>
+        <v>26119800</v>
       </c>
       <c r="F76" s="3">
-        <v>21700700</v>
+        <v>23989100</v>
       </c>
       <c r="G76" s="3">
-        <v>18784400</v>
+        <v>21540100</v>
       </c>
       <c r="H76" s="3">
-        <v>14656800</v>
+        <v>16329400</v>
       </c>
       <c r="I76" s="3">
-        <v>13619000</v>
+        <v>16490400</v>
       </c>
       <c r="J76" s="3">
-        <v>13187100</v>
+        <v>17000300</v>
       </c>
       <c r="K76" s="3">
         <v>12545400</v>
@@ -3631,25 +3631,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>5275400</v>
+        <v>5311700</v>
       </c>
       <c r="E81" s="3">
-        <v>4057200</v>
+        <v>4144700</v>
       </c>
       <c r="F81" s="3">
-        <v>2993100</v>
+        <v>3308800</v>
       </c>
       <c r="G81" s="3">
-        <v>2191400</v>
+        <v>2512900</v>
       </c>
       <c r="H81" s="3">
-        <v>1140300</v>
+        <v>1270400</v>
       </c>
       <c r="I81" s="3">
-        <v>507100</v>
+        <v>614000</v>
       </c>
       <c r="J81" s="3">
-        <v>919300</v>
+        <v>1185100</v>
       </c>
       <c r="K81" s="3">
         <v>1221600</v>
@@ -3695,25 +3695,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>237900</v>
+        <v>229800</v>
       </c>
       <c r="E83" s="3">
-        <v>196200</v>
+        <v>189900</v>
       </c>
       <c r="F83" s="3">
-        <v>176400</v>
+        <v>193700</v>
       </c>
       <c r="G83" s="3">
-        <v>175400</v>
+        <v>201100</v>
       </c>
       <c r="H83" s="3">
-        <v>163300</v>
+        <v>181900</v>
       </c>
       <c r="I83" s="3">
-        <v>124600</v>
+        <v>150900</v>
       </c>
       <c r="J83" s="3">
-        <v>123900</v>
+        <v>159700</v>
       </c>
       <c r="K83" s="3">
         <v>125200</v>
@@ -3965,25 +3965,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>18840200</v>
+        <v>-9086600</v>
       </c>
       <c r="E89" s="3">
-        <v>-449500</v>
+        <v>-15006900</v>
       </c>
       <c r="F89" s="3">
-        <v>6860300</v>
+        <v>-9660600</v>
       </c>
       <c r="G89" s="3">
-        <v>16451400</v>
+        <v>-2889600</v>
       </c>
       <c r="H89" s="3">
-        <v>9484100</v>
+        <v>-5299200</v>
       </c>
       <c r="I89" s="3">
-        <v>5801600</v>
+        <v>-6761900</v>
       </c>
       <c r="J89" s="3">
-        <v>2310400</v>
+        <v>-8271400</v>
       </c>
       <c r="K89" s="3">
         <v>6311000</v>
@@ -4029,25 +4029,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-438500</v>
+        <v>-441500</v>
       </c>
       <c r="E91" s="3">
-        <v>-294100</v>
+        <v>-300500</v>
       </c>
       <c r="F91" s="3">
-        <v>-221700</v>
+        <v>-245100</v>
       </c>
       <c r="G91" s="3">
-        <v>-201200</v>
+        <v>-230800</v>
       </c>
       <c r="H91" s="3">
-        <v>-223300</v>
+        <v>-248800</v>
       </c>
       <c r="I91" s="3">
-        <v>-136900</v>
+        <v>-165700</v>
       </c>
       <c r="J91" s="3">
-        <v>-124200</v>
+        <v>-160100</v>
       </c>
       <c r="K91" s="3">
         <v>-157900</v>
@@ -4164,25 +4164,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-17395000</v>
+        <v>-17514800</v>
       </c>
       <c r="E94" s="3">
-        <v>-8106200</v>
+        <v>-8281100</v>
       </c>
       <c r="F94" s="3">
-        <v>-4687100</v>
+        <v>-5181400</v>
       </c>
       <c r="G94" s="3">
-        <v>-7508000</v>
+        <v>-8609500</v>
       </c>
       <c r="H94" s="3">
-        <v>-5043200</v>
+        <v>-5618700</v>
       </c>
       <c r="I94" s="3">
-        <v>-3593500</v>
+        <v>-4351200</v>
       </c>
       <c r="J94" s="3">
-        <v>-6028400</v>
+        <v>-7771600</v>
       </c>
       <c r="K94" s="3">
         <v>-192500</v>
@@ -4228,25 +4228,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-667400</v>
+        <v>672000</v>
       </c>
       <c r="E96" s="3">
-        <v>-414700</v>
+        <v>423700</v>
       </c>
       <c r="F96" s="3">
-        <v>-165100</v>
+        <v>182500</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-105700</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-139300</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>-204600</v>
+        <v>0</v>
       </c>
       <c r="K96" s="3">
         <v>-410400</v>
@@ -4408,25 +4408,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1640700</v>
+        <v>29616100</v>
       </c>
       <c r="E100" s="3">
-        <v>2955100</v>
+        <v>17566400</v>
       </c>
       <c r="F100" s="3">
-        <v>2080200</v>
+        <v>19617500</v>
       </c>
       <c r="G100" s="3">
-        <v>-6516300</v>
+        <v>14282200</v>
       </c>
       <c r="H100" s="3">
-        <v>356700</v>
+        <v>16263000</v>
       </c>
       <c r="I100" s="3">
-        <v>-2383700</v>
+        <v>10900400</v>
       </c>
       <c r="J100" s="3">
-        <v>4729400</v>
+        <v>17346900</v>
       </c>
       <c r="K100" s="3">
         <v>-4252800</v>
@@ -4453,25 +4453,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>50500</v>
+        <v>50800</v>
       </c>
       <c r="E101" s="3">
-        <v>37700</v>
+        <v>38500</v>
       </c>
       <c r="F101" s="3">
-        <v>-15100</v>
+        <v>-16700</v>
       </c>
       <c r="G101" s="3">
-        <v>-76800</v>
+        <v>-88000</v>
       </c>
       <c r="H101" s="3">
-        <v>25500</v>
+        <v>28400</v>
       </c>
       <c r="I101" s="3">
-        <v>-16000</v>
+        <v>-19400</v>
       </c>
       <c r="J101" s="3">
-        <v>2700</v>
+        <v>3500</v>
       </c>
       <c r="K101" s="3">
         <v>-12600</v>
@@ -4498,25 +4498,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>3136400</v>
+        <v>3065500</v>
       </c>
       <c r="E102" s="3">
-        <v>-5563000</v>
+        <v>-5683000</v>
       </c>
       <c r="F102" s="3">
-        <v>4238200</v>
+        <v>4758800</v>
       </c>
       <c r="G102" s="3">
-        <v>2350300</v>
+        <v>2695100</v>
       </c>
       <c r="H102" s="3">
-        <v>4823100</v>
+        <v>5373500</v>
       </c>
       <c r="I102" s="3">
-        <v>-191700</v>
+        <v>-232100</v>
       </c>
       <c r="J102" s="3">
-        <v>1014200</v>
+        <v>1307500</v>
       </c>
       <c r="K102" s="3">
         <v>1853000</v>

--- a/AAII_Financials/Yearly/IBN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IBN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
   <si>
     <t>IBN</t>
   </si>
@@ -656,118 +656,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44651</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44286</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43921</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43555</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43190</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42825</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42460</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42094</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41729</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41364</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40999</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>23482900</v>
+      </c>
+      <c r="E8" s="3">
         <v>17137800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14235400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>13036700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>13189100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>10965300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10343800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10255000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7306700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7168600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7101300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6798400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5933700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5494100</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -810,36 +816,39 @@
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>23482900</v>
+      </c>
+      <c r="E10" s="3">
         <v>17137800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>14235400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>13036700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>13189100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>10965300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>10343800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>10255000</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -855,9 +864,12 @@
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,8 +887,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -919,9 +932,12 @@
       <c r="P12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,9 +980,12 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -991,8 +1010,8 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1009,54 +1028,60 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>314900</v>
+      </c>
+      <c r="E15" s="3">
         <v>229800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>189900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>193700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>201100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>181900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>150900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>159700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-109300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-101900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-103100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-98800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-82700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-97100</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,98 +1096,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14956700</v>
+      </c>
+      <c r="E17" s="3">
         <v>11736000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10038800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9639200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10425300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9497800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9274600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8567900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6064700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5043400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4644600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4423200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3944400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3768900</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>8526200</v>
+      </c>
+      <c r="E18" s="3">
         <v>5401800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4196600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3397500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2763800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1467500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1069200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1687000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1242000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2125200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2456700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2375200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1989300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1725200</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,83 +1212,87 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-128900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-121600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-99400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-19700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-23300</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>413700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-395800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-88000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-138100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-189200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-179900</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8858700</v>
+      </c>
+      <c r="E21" s="3">
         <v>5760400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4508100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3690600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2984600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1672700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1220100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1846700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1780700</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1266,12 +1302,15 @@
       <c r="O21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="3">
         <v>1654500</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1296,8 +1335,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1314,59 +1353,65 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>8543800</v>
+      </c>
+      <c r="E23" s="3">
         <v>5530600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4318200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3496900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2783500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1490800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1069200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1687000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1655700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1729400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2368700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2237100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1800100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1545300</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>5</v>
+      <c r="D24" s="3">
+        <v>2157500</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>5</v>
@@ -1380,33 +1425,36 @@
       <c r="H24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I24" s="3">
+      <c r="I24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="3">
         <v>248100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>288700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>296000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>408300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>696600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>633300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>461000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>397500</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,99 +1497,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6386400</v>
+      </c>
+      <c r="E26" s="3">
         <v>5530600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4318200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3496900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2783500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1490800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>821100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1398300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1359700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1321100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1672100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1603700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1339200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1147800</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5972100</v>
+      </c>
+      <c r="E27" s="3">
         <v>5311700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4144700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3308800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2512900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1270400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>614000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1185100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1221600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1230800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1582300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1516400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1335900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1023900</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1611,8 +1671,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>5</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>5</v>
@@ -1623,15 +1683,18 @@
       <c r="N29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,99 +1785,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E32" s="3">
         <v>128900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>121600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>99400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>19700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>23300</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>-413700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>395800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>88000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>138100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>189200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>179900</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5972100</v>
+      </c>
+      <c r="E33" s="3">
         <v>5311700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4144700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3308800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2512900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1270400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>614000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1185100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1221600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1230800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1582300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1516400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1335900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1023900</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,104 +1929,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5972100</v>
+      </c>
+      <c r="E35" s="3">
         <v>5311700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4144700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3308800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2512900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1270400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>614000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1185100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1221600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1230800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1582300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1516400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1335900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1023900</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44651</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44286</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43921</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43555</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43190</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42825</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42460</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42094</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41729</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41364</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40999</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,68 +2073,72 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>25047600</v>
+      </c>
+      <c r="E41" s="3">
         <v>9815500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9314200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10636800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>14818200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>13613700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8405300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9825300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6957800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6136300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5980200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5999100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2554200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2997300</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>2040200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2167800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1388200</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -2060,26 +2149,29 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>27788600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>18542900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>22171000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>22326800</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2101,12 +2193,12 @@
       <c r="I43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K43" s="3">
         <v>61300</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
@@ -2122,9 +2214,12 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2143,15 +2238,15 @@
       <c r="H44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3">
         <v>144900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>303500</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
@@ -2167,36 +2262,39 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3">
         <v>3526600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2756500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2302400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2582000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2882300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3134000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2673500</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -2212,36 +2310,39 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>25047600</v>
+      </c>
+      <c r="E46" s="3">
         <v>25102600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>21540900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>27821100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>22752900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>19861500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>15892100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>16714600</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2257,42 +2358,45 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>103734500</v>
+      </c>
+      <c r="E47" s="3">
         <v>79492500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>60337200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>54846800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>54405300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>46001100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>41459900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>42213700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>45100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>44700</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>5</v>
       </c>
@@ -2302,99 +2406,108 @@
       <c r="P47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1850600</v>
+      </c>
+      <c r="E48" s="3">
         <v>1589100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1335700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1397500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1477500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1382300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1394300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1454500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1119600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1053500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>758600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>756600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>724100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>785500</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>990000</v>
+      </c>
+      <c r="E49" s="3">
         <v>297000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>12300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>13400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>15800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>17200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>15200</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
       <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3">
         <v>19700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>18900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>20700</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,54 +2598,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11341100</v>
+      </c>
+      <c r="E52" s="3">
         <v>25179200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>22350600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>24549900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>26964000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>20687500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>25079200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>24057700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1346000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>599800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>208500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>127800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>354600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>405400</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,54 +2694,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>309226900</v>
+      </c>
+      <c r="E54" s="3">
         <v>283737700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>238489000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>230945100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>215118900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>182907800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>178796800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>172767000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>118188000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>111078000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>106729000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>102743000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>89278900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>89548900</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,80 +2785,84 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>192124100</v>
+      </c>
+      <c r="E57" s="3">
         <v>180931000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>150402200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>146530400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>136243400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>111000800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>103198700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>94311000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3179300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2412900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2288200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2637600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2609300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2105500</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>14551100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12577700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1192900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>578600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>430700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>275600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>198300</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -2745,81 +2878,87 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="3">
         <v>1543600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1695900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1780300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1800800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>857700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1256200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1143700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>397300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>422500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>407000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>349000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>311500</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>192124100</v>
+      </c>
+      <c r="E60" s="3">
         <v>197493700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>165082400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>149866300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>138962100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>112697000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>105259500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>96204600</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -2835,99 +2974,108 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>25616400</v>
+      </c>
+      <c r="E61" s="3">
         <v>12469600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12691300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>21601200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>19102800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>27973700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>30080800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>35053700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>22430800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>26538500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>27293800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>25218700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>22873100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>23323500</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>53012900</v>
+      </c>
+      <c r="E62" s="3">
         <v>41364900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>33781200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>34700400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>34203300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>25005400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>26016500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>23585100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>306000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>352800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>329600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>294600</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,54 +3214,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>270753400</v>
+      </c>
+      <c r="E66" s="3">
         <v>251328100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>211554900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>206167900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>192268200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>165676100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>161356700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>154843400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>105643000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>99699600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>95785600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>92241100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>80181600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>80688300</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,9 +3378,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3259,9 +3426,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,54 +3474,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E72" s="3">
         <v>21618800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>17217300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>14606300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>12156700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9235900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8927700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9047000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7922300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6759100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6373200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5639000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4568300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>4003000</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,54 +3666,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>36737000</v>
+      </c>
+      <c r="E76" s="3">
         <v>30742700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>26119800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>23989100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>21540100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16329400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16490400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>17000300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12545400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11378000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10943800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10501500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9097300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8860600</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,104 +3762,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44651</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44286</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43921</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43555</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43190</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42825</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42460</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42094</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41729</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41364</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40999</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5972100</v>
+      </c>
+      <c r="E81" s="3">
         <v>5311700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4144700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3308800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2512900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1270400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>614000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1185100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1221600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1230800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1582300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1516400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1335900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1023900</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,38 +3886,39 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>314900</v>
+      </c>
+      <c r="E83" s="3">
         <v>229800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>189900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>193700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>201100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>181900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>150900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>159700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>125200</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>5</v>
       </c>
@@ -3730,12 +3928,15 @@
       <c r="O83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q83" s="3">
         <v>109100</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,54 +4171,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8806900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-9086600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-15006900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-9660600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2889600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5299200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6761900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-8271400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6311000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1483800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>874000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>929500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2312700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-985300</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,53 +4242,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-558200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-441500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-245100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-230800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-248800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-165700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-160100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-157900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-150500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-108200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-115100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-82600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-87500</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,39 +4383,42 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-9045200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-17514800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8281100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5181400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-8609500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5618700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4351200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7771600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-192500</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>5</v>
       </c>
@@ -4199,12 +4428,15 @@
       <c r="O94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-3074600</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,23 +4454,24 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>824100</v>
+      </c>
+      <c r="E96" s="3">
         <v>672000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>423700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>182500</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
@@ -4249,26 +4482,29 @@
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-410400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-372900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-349400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-371500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-293400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-274900</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,39 +4643,42 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>23833200</v>
+      </c>
+      <c r="E100" s="3">
         <v>29616100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>17566400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>19617500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>14282200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>16263000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>10900400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>17346900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4252800</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>5</v>
       </c>
@@ -4443,42 +4688,45 @@
       <c r="O100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="3">
         <v>4256900</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E101" s="3">
         <v>50800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>38500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-16700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-88000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>28400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-19400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-12600</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>5</v>
       </c>
@@ -4488,55 +4736,61 @@
       <c r="O101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="3">
         <v>59100</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5998400</v>
+      </c>
+      <c r="E102" s="3">
         <v>3065500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5683000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4758800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2695100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5373500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-232100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1307500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1853000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-75100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-143800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-152900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1086000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>256100</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/IBN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IBN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
   <si>
     <t>IBN</t>
   </si>
@@ -730,7 +730,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>23482900</v>
+        <v>21325400</v>
       </c>
       <c r="E8" s="3">
         <v>17137800</v>
@@ -826,7 +826,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>23482900</v>
+        <v>21325400</v>
       </c>
       <c r="E10" s="3">
         <v>17137800</v>
@@ -1041,10 +1041,10 @@
         <v>314900</v>
       </c>
       <c r="E15" s="3">
-        <v>229800</v>
+        <v>239500</v>
       </c>
       <c r="F15" s="3">
-        <v>189900</v>
+        <v>199100</v>
       </c>
       <c r="G15" s="3">
         <v>193700</v>
@@ -1151,7 +1151,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>8526200</v>
+        <v>6368700</v>
       </c>
       <c r="E18" s="3">
         <v>5401800</v>
@@ -1267,13 +1267,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>8858700</v>
+        <v>6701200</v>
       </c>
       <c r="E21" s="3">
-        <v>5760400</v>
+        <v>5770200</v>
       </c>
       <c r="F21" s="3">
-        <v>4508100</v>
+        <v>4517300</v>
       </c>
       <c r="G21" s="3">
         <v>3690600</v>
@@ -1363,7 +1363,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>8543800</v>
+        <v>6386400</v>
       </c>
       <c r="E23" s="3">
         <v>5530600</v>
@@ -1410,8 +1410,8 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>2157500</v>
+      <c r="D24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>5</v>
@@ -1843,7 +1843,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>5972100</v>
+        <v>5972000</v>
       </c>
       <c r="E33" s="3">
         <v>5311700</v>
@@ -1939,7 +1939,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>5972100</v>
+        <v>5972000</v>
       </c>
       <c r="E35" s="3">
         <v>5311700</v>
@@ -2080,7 +2080,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>25047600</v>
+        <v>11735500</v>
       </c>
       <c r="E41" s="3">
         <v>9815500</v>
@@ -2128,7 +2128,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>1891800</v>
       </c>
       <c r="E42" s="3">
         <v>2040200</v>
@@ -2271,8 +2271,8 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>5</v>
+      <c r="D45" s="3">
+        <v>4133400</v>
       </c>
       <c r="E45" s="3">
         <v>3526600</v>
@@ -2320,7 +2320,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>25047600</v>
+        <v>31072800</v>
       </c>
       <c r="E46" s="3">
         <v>25102600</v>
@@ -2368,7 +2368,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>103734500</v>
+        <v>84864200</v>
       </c>
       <c r="E47" s="3">
         <v>79492500</v>
@@ -2608,7 +2608,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>11341100</v>
+        <v>23619600</v>
       </c>
       <c r="E52" s="3">
         <v>25179200</v>
@@ -2792,7 +2792,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>192124100</v>
+        <v>199371500</v>
       </c>
       <c r="E57" s="3">
         <v>180931000</v>
@@ -2840,7 +2840,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>16917600</v>
       </c>
       <c r="E58" s="3">
         <v>14551100</v>
@@ -2887,8 +2887,8 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>5</v>
+      <c r="D59" s="3">
+        <v>1059300</v>
       </c>
       <c r="E59" s="3">
         <v>1543600</v>
@@ -2936,7 +2936,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>192124100</v>
+        <v>217841800</v>
       </c>
       <c r="E60" s="3">
         <v>197493700</v>
@@ -2984,7 +2984,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>25616400</v>
+        <v>10888200</v>
       </c>
       <c r="E61" s="3">
         <v>12469600</v>
@@ -3032,7 +3032,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>53012900</v>
+        <v>42023500</v>
       </c>
       <c r="E62" s="3">
         <v>41364900</v>
@@ -3483,11 +3483,11 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>5</v>
+      <c r="D72" s="3">
+        <v>26434600</v>
       </c>
       <c r="E72" s="3">
-        <v>21618800</v>
+        <v>21622800</v>
       </c>
       <c r="F72" s="3">
         <v>17217300</v>
@@ -3825,7 +3825,7 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>5972100</v>
+        <v>5972000</v>
       </c>
       <c r="E81" s="3">
         <v>5311700</v>
@@ -3896,10 +3896,10 @@
         <v>314900</v>
       </c>
       <c r="E83" s="3">
-        <v>229800</v>
+        <v>239500</v>
       </c>
       <c r="F83" s="3">
-        <v>189900</v>
+        <v>199100</v>
       </c>
       <c r="G83" s="3">
         <v>193700</v>
